--- a/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2584.62</v>
+        <v>41231.7</v>
       </c>
       <c r="C4" t="n">
-        <v>560448</v>
+        <v>6525288</v>
       </c>
       <c r="D4" t="n">
-        <v>440352</v>
+        <v>5127012</v>
       </c>
       <c r="E4" t="n">
-        <v>123300</v>
+        <v>1458000</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>6450</v>
+        <v>111720</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>10890</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>19200</v>
+        <v>286650</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3678.21</v>
+        <v>37385.73</v>
       </c>
       <c r="C5" t="n">
-        <v>589680</v>
+        <v>3582936</v>
       </c>
       <c r="D5" t="n">
-        <v>463320</v>
+        <v>2815164</v>
       </c>
       <c r="E5" t="n">
-        <v>95400</v>
+        <v>521100</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>9480</v>
+        <v>80970</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>11970</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>22620</v>
+        <v>180240</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3666.6</v>
+        <v>23058.54</v>
       </c>
       <c r="C6" t="n">
-        <v>355320</v>
+        <v>1380960</v>
       </c>
       <c r="D6" t="n">
-        <v>279180</v>
+        <v>1085040</v>
       </c>
       <c r="E6" t="n">
-        <v>58500</v>
+        <v>95400</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>6210</v>
+        <v>42390</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>18240</v>
+        <v>76770</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2394.99</v>
+        <v>6501.69</v>
       </c>
       <c r="C7" t="n">
-        <v>169344</v>
+        <v>475272</v>
       </c>
       <c r="D7" t="n">
-        <v>133056</v>
+        <v>373428</v>
       </c>
       <c r="E7" t="n">
-        <v>23400</v>
+        <v>19800</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4740</v>
+        <v>10410</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7230</v>
+        <v>36030</v>
       </c>
     </row>
     <row r="8">
@@ -9995,22 +9989,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1268.46</v>
+        <v>1153.71</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>104328</v>
       </c>
       <c r="D8" t="n">
-        <v>41184</v>
+        <v>81972</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>1800</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1410</v>
+        <v>1560</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -10025,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3570</v>
+        <v>10440</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>621.63</v>
+        <v>231.3</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>16128</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>12672</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>900</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>480</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>810</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="10">
@@ -10071,7 +10065,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>383.04</v>
+        <v>181.53</v>
       </c>
       <c r="C10" t="n">
         <v>2016</v>
@@ -10080,16 +10074,16 @@
         <v>1584</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>480</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.01</v>
+        <v>58.59</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>1512</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>1188</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="12">
@@ -10147,13 +10141,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>24.3</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>2016</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>1584</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10162,7 +10156,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.57</v>
+        <v>14.22</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1584</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -10223,13 +10217,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>6.84</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -10238,7 +10232,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>3.69</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,7 +10331,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1655.19</v>
+        <v>16823.58</v>
       </c>
       <c r="C5" t="n">
-        <v>324324</v>
+        <v>1970614.8</v>
       </c>
       <c r="D5" t="n">
-        <v>153358.92</v>
+        <v>931819.28</v>
       </c>
       <c r="E5" t="n">
-        <v>10522.62</v>
+        <v>57477.33</v>
       </c>
       <c r="F5" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4309.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4750.2</v>
+        <v>37850.4</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>2933.28</v>
+        <v>18446.83</v>
       </c>
       <c r="C6" t="n">
-        <v>319788</v>
+        <v>1242864</v>
       </c>
       <c r="D6" t="n">
-        <v>141544.26</v>
+        <v>550115.28</v>
       </c>
       <c r="E6" t="n">
-        <v>9886.5</v>
+        <v>16122.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>310.5</v>
+        <v>2119.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>786.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6748.8</v>
+        <v>28404.9</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2275.24</v>
+        <v>6176.61</v>
       </c>
       <c r="C7" t="n">
-        <v>169344</v>
+        <v>475272</v>
       </c>
       <c r="D7" t="n">
-        <v>84889.73</v>
+        <v>238247.06</v>
       </c>
       <c r="E7" t="n">
-        <v>4977.18</v>
+        <v>4211.46</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>711</v>
+        <v>1561.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>306.6</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4338</v>
+        <v>21618</v>
       </c>
     </row>
     <row r="8">
@@ -11859,22 +11853,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1268.46</v>
+        <v>1153.71</v>
       </c>
       <c r="C8" t="n">
-        <v>52416</v>
+        <v>104328</v>
       </c>
       <c r="D8" t="n">
-        <v>30311.42</v>
+        <v>60331.39</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>441.54</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>916.5</v>
+        <v>1014</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11889,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2534.7</v>
+        <v>7412.4</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>621.63</v>
+        <v>231.3</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>16128</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>10175.62</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>240.93</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>408</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>656.1</v>
+        <v>2891.7</v>
       </c>
     </row>
     <row r="10">
@@ -11935,7 +11929,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>383.04</v>
+        <v>181.53</v>
       </c>
       <c r="C10" t="n">
         <v>2016</v>
@@ -11944,16 +11938,16 @@
         <v>1378.08</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>427.2</v>
+        <v>2643.3</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>215.01</v>
+        <v>58.59</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>1512</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>1067.42</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="12">
@@ -12011,13 +12005,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>24.3</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>2016</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>1468.37</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12026,7 +12020,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>168.57</v>
+        <v>14.22</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1504.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -12087,13 +12081,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.84</v>
+        <v>6.84</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -12102,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>420</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>3.69</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>390.46</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>0.45</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,7 +12195,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3630</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3641427.9</v>
+        <v>37011872.7</v>
       </c>
       <c r="C5" t="n">
-        <v>17837820</v>
+        <v>108383814</v>
       </c>
       <c r="D5" t="n">
-        <v>15539859.36</v>
+        <v>94421248.05</v>
       </c>
       <c r="E5" t="n">
-        <v>1938687.51</v>
+        <v>10589623.28</v>
       </c>
       <c r="F5" t="n">
-        <v>5000.04</v>
+        <v>5833.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1192140.18</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>44746.88</v>
+        <v>356550.77</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6453216</v>
+        <v>40583030.4</v>
       </c>
       <c r="C6" t="n">
-        <v>17588340</v>
+        <v>68357520</v>
       </c>
       <c r="D6" t="n">
-        <v>14342679.87</v>
+        <v>55743181.32</v>
       </c>
       <c r="E6" t="n">
-        <v>1821488.76</v>
+        <v>2970427.82</v>
       </c>
       <c r="F6" t="n">
-        <v>12500.1</v>
+        <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5744.25</v>
+        <v>39210.75</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>217612.89</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>29166.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>63573.7</v>
+        <v>267574.16</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5005529.1</v>
+        <v>13588532.1</v>
       </c>
       <c r="C7" t="n">
-        <v>9313920</v>
+        <v>26139960</v>
       </c>
       <c r="D7" t="n">
-        <v>8601876.140000001</v>
+        <v>24141575</v>
       </c>
       <c r="E7" t="n">
-        <v>916995.64</v>
+        <v>775919.39</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13153.5</v>
+        <v>28887.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>84820.89</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>81666.2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>40863.96</v>
+        <v>203641.56</v>
       </c>
     </row>
     <row r="8">
@@ -12791,22 +12785,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2790612</v>
+        <v>2538162</v>
       </c>
       <c r="C8" t="n">
-        <v>2882880</v>
+        <v>5738040</v>
       </c>
       <c r="D8" t="n">
-        <v>3071456.59</v>
+        <v>6113379.95</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>81349.33</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>16955.25</v>
+        <v>18759</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12821,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23876.87</v>
+        <v>69824.81</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1367586</v>
+        <v>508860</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>887040</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>1031095.17</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>44388.94</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>7548</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6180.46</v>
+        <v>27239.81</v>
       </c>
     </row>
     <row r="10">
@@ -12867,7 +12861,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>842688</v>
+        <v>399366</v>
       </c>
       <c r="C10" t="n">
         <v>110880</v>
@@ -12876,16 +12870,16 @@
         <v>139640.85</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>48086.64</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>6660</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4024.22</v>
+        <v>24899.89</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>473022</v>
+        <v>128898</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>83160</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>108161.47</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>22042.8</v>
       </c>
     </row>
     <row r="12">
@@ -12943,13 +12937,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345510</v>
+        <v>53460</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>110880</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>148789.73</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12958,7 +12952,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>3330</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>6782.4</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>370854</v>
+        <v>31284</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>110880</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>152401.13</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2775</v>
+        <v>1110</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>565.2</v>
       </c>
     </row>
     <row r="14">
@@ -13019,13 +13013,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94248</v>
+        <v>15048</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13034,7 +13028,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>7770</v>
+        <v>2775</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>2260.8</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>8118</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>39564.91</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>990</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,7 +13127,7 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5369.4</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>67155</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="19">
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>120380.04</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>41231.7</v>
+        <v>16882.11</v>
       </c>
       <c r="C4" t="n">
-        <v>6525288</v>
+        <v>1827504</v>
       </c>
       <c r="D4" t="n">
-        <v>5127012</v>
+        <v>1435896</v>
       </c>
       <c r="E4" t="n">
-        <v>1458000</v>
+        <v>731700</v>
       </c>
       <c r="F4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>111720</v>
+        <v>50160</v>
       </c>
       <c r="H4" t="n">
-        <v>10890</v>
+        <v>3990</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>286650</v>
+        <v>177420</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>37385.73</v>
+        <v>3605.67</v>
       </c>
       <c r="C5" t="n">
-        <v>3582936</v>
+        <v>333648</v>
       </c>
       <c r="D5" t="n">
-        <v>2815164</v>
+        <v>262152</v>
       </c>
       <c r="E5" t="n">
-        <v>521100</v>
+        <v>166500</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>80970</v>
+        <v>10080</v>
       </c>
       <c r="H5" t="n">
-        <v>11970</v>
+        <v>1050</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>180240</v>
+        <v>47370</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>23058.54</v>
+        <v>304.83</v>
       </c>
       <c r="C6" t="n">
-        <v>1380960</v>
+        <v>46872</v>
       </c>
       <c r="D6" t="n">
-        <v>1085040</v>
+        <v>36828</v>
       </c>
       <c r="E6" t="n">
-        <v>95400</v>
+        <v>15300</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>42390</v>
+        <v>750</v>
       </c>
       <c r="H6" t="n">
-        <v>1380</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>76770</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6501.69</v>
+        <v>79.83</v>
       </c>
       <c r="C7" t="n">
-        <v>475272</v>
+        <v>7056</v>
       </c>
       <c r="D7" t="n">
-        <v>373428</v>
+        <v>5544</v>
       </c>
       <c r="E7" t="n">
-        <v>19800</v>
+        <v>1800</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10410</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>36030</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -13723,22 +13717,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1153.71</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>104328</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>81972</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1560</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -13753,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>10440</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>231.3</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>16128</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>12672</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3570</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13799,25 +13793,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>181.53</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2970</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>58.59</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,7 +13846,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2340</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -13875,13 +13869,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -13890,7 +13884,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>14.22</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,13 +13945,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13966,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14106,10 +14100,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>16823.58</v>
+        <v>1622.55</v>
       </c>
       <c r="C5" t="n">
-        <v>1970614.8</v>
+        <v>183506.4</v>
       </c>
       <c r="D5" t="n">
-        <v>931819.28</v>
+        <v>86772.31</v>
       </c>
       <c r="E5" t="n">
-        <v>57477.33</v>
+        <v>18364.95</v>
       </c>
       <c r="F5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4309.2</v>
+        <v>378</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>37850.4</v>
+        <v>9947.700000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>18446.83</v>
+        <v>243.86</v>
       </c>
       <c r="C6" t="n">
-        <v>1242864</v>
+        <v>42184.8</v>
       </c>
       <c r="D6" t="n">
-        <v>550115.28</v>
+        <v>18671.8</v>
       </c>
       <c r="E6" t="n">
-        <v>16122.6</v>
+        <v>2585.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2119.5</v>
+        <v>37.5</v>
       </c>
       <c r="H6" t="n">
-        <v>786.6</v>
+        <v>119.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>28404.9</v>
+        <v>3085.8</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6176.61</v>
+        <v>75.84</v>
       </c>
       <c r="C7" t="n">
-        <v>475272</v>
+        <v>7056</v>
       </c>
       <c r="D7" t="n">
-        <v>238247.06</v>
+        <v>3537.07</v>
       </c>
       <c r="E7" t="n">
-        <v>4211.46</v>
+        <v>382.86</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1561.5</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>306.6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>21618</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8">
@@ -14655,22 +14649,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1153.71</v>
+        <v>2.7</v>
       </c>
       <c r="C8" t="n">
-        <v>104328</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>60331.39</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>441.54</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1014</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14685,7 +14679,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7412.4</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>231.3</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>16128</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>10175.62</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>240.93</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>408</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2891.7</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14731,25 +14725,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>181.53</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2643.3</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>58.59</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,7 +14778,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2340</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -14807,13 +14801,13 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -14822,7 +14816,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>14.22</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1504.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,13 +14877,13 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>6.84</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -14898,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>390.46</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15038,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3630</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>37011872.7</v>
+        <v>3569613.3</v>
       </c>
       <c r="C5" t="n">
-        <v>108383814</v>
+        <v>10092852</v>
       </c>
       <c r="D5" t="n">
-        <v>94421248.05</v>
+        <v>8792638.369999999</v>
       </c>
       <c r="E5" t="n">
-        <v>10589623.28</v>
+        <v>3383558.39</v>
       </c>
       <c r="F5" t="n">
-        <v>5833.38</v>
+        <v>5000.04</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1192140.18</v>
+        <v>104573.7</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>356550.77</v>
+        <v>93707.33</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>40583030.4</v>
+        <v>536500.8</v>
       </c>
       <c r="C6" t="n">
-        <v>68357520</v>
+        <v>2320164</v>
       </c>
       <c r="D6" t="n">
-        <v>55743181.32</v>
+        <v>1892013.09</v>
       </c>
       <c r="E6" t="n">
-        <v>2970427.82</v>
+        <v>476389.37</v>
       </c>
       <c r="F6" t="n">
-        <v>8333.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>39210.75</v>
+        <v>693.75</v>
       </c>
       <c r="H6" t="n">
-        <v>217612.89</v>
+        <v>33115</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>267574.16</v>
+        <v>29068.24</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>13588532.1</v>
+        <v>166844.7</v>
       </c>
       <c r="C7" t="n">
-        <v>26139960</v>
+        <v>388080</v>
       </c>
       <c r="D7" t="n">
-        <v>24141575</v>
+        <v>358411.51</v>
       </c>
       <c r="E7" t="n">
-        <v>775919.39</v>
+        <v>70538.13</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>28887.75</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>203641.56</v>
+        <v>3221.64</v>
       </c>
     </row>
     <row r="8">
@@ -15587,22 +15581,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2538162</v>
+        <v>5940</v>
       </c>
       <c r="C8" t="n">
-        <v>5738040</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>6113379.95</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>81349.33</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18759</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15617,7 +15611,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>69824.81</v>
+        <v>601.9400000000001</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>508860</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>887040</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1031095.17</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7548</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>27239.81</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="10">
@@ -15663,25 +15657,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>399366</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6660</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24899.89</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,13 +15695,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>128898</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15716,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>22042.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>53460</v>
-      </c>
-      <c r="C12" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D12" t="n">
-        <v>148789.73</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6782.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>31284</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>565.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15048</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2260.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>8118</v>
-      </c>
-      <c r="C15" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D15" t="n">
-        <v>39564.91</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>990</v>
-      </c>
-      <c r="C16" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D16" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>5369.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D18" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>67155</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D19" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D20" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5096.16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>862344</v>
-      </c>
-      <c r="D4" t="n">
-        <v>677556</v>
-      </c>
-      <c r="E4" t="n">
-        <v>236700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13680</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3240</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>32400</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5988.42</v>
-      </c>
-      <c r="C5" t="n">
-        <v>595224</v>
-      </c>
-      <c r="D5" t="n">
-        <v>467676</v>
-      </c>
-      <c r="E5" t="n">
-        <v>108000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9270</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26460</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5197.14</v>
-      </c>
-      <c r="C6" t="n">
-        <v>319032</v>
-      </c>
-      <c r="D6" t="n">
-        <v>250668</v>
-      </c>
-      <c r="E6" t="n">
-        <v>54900</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5910</v>
-      </c>
-      <c r="H6" t="n">
-        <v>150</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15360</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3733.47</v>
-      </c>
-      <c r="C7" t="n">
-        <v>177912</v>
-      </c>
-      <c r="D7" t="n">
-        <v>139788</v>
-      </c>
-      <c r="E7" t="n">
-        <v>18900</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3510</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>13440</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2569.23</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59472</v>
-      </c>
-      <c r="D8" t="n">
-        <v>46728</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4920</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1705.95</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28728</v>
-      </c>
-      <c r="D9" t="n">
-        <v>22572</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>330</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>886.05</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4356</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>528.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.62</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.22</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>240.03</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2694.79</v>
-      </c>
-      <c r="C5" t="n">
-        <v>327373.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>154800.76</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11912.4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>432</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5556.6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4157.71</v>
-      </c>
-      <c r="C6" t="n">
-        <v>287128.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>127088.68</v>
-      </c>
-      <c r="E6" t="n">
-        <v>9278.1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>295.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5683.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3546.8</v>
-      </c>
-      <c r="C7" t="n">
-        <v>177912</v>
-      </c>
-      <c r="D7" t="n">
-        <v>89184.74000000001</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4020.03</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>526.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8064</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2569.23</v>
-      </c>
-      <c r="C8" t="n">
-        <v>59472</v>
-      </c>
-      <c r="D8" t="n">
-        <v>34391.81</v>
-      </c>
-      <c r="E8" t="n">
-        <v>662.3099999999999</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1443</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3493.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1705.95</v>
-      </c>
-      <c r="C9" t="n">
-        <v>28728</v>
-      </c>
-      <c r="D9" t="n">
-        <v>18125.32</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>280.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>826.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>886.05</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5544</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3789.72</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>210</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>528.3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>397.62</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.22</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>240.03</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26.64</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5928535.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>18005526</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15685960.61</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2194740.58</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>119512.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>52343.17</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>9146966.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>15792084</v>
-      </c>
-      <c r="D6" t="n">
-        <v>12877895.54</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1709397.14</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5466.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>23653.57</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>53535.74</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7802952.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9785160</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9037090.109999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>740650.33</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9740.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>75962.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5652306</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3270960</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3484921.9</v>
-      </c>
-      <c r="E8" t="n">
-        <v>122023.99</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>26695.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>32905.94</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3753090</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1580040</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1836638.27</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5189.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7782.8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>1949310</v>
-      </c>
-      <c r="C10" t="n">
-        <v>304920</v>
-      </c>
-      <c r="D10" t="n">
-        <v>384012.33</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1162260</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>874764</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>810414</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1080684</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>528066</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>94446</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>58608</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>16882.11</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1827504</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1435896</v>
-      </c>
-      <c r="E4" t="n">
-        <v>731700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>50160</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3990</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>177420</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3605.67</v>
-      </c>
-      <c r="C5" t="n">
-        <v>333648</v>
-      </c>
-      <c r="D5" t="n">
-        <v>262152</v>
-      </c>
-      <c r="E5" t="n">
-        <v>166500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10080</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1050</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47370</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>304.83</v>
-      </c>
-      <c r="C6" t="n">
-        <v>46872</v>
-      </c>
-      <c r="D6" t="n">
-        <v>36828</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>750</v>
-      </c>
-      <c r="H6" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8340</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>79.83</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7056</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5544</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>1622.55</v>
-      </c>
-      <c r="C5" t="n">
-        <v>183506.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>86772.31</v>
-      </c>
-      <c r="E5" t="n">
-        <v>18364.95</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>378</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>9947.700000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>243.86</v>
-      </c>
-      <c r="C6" t="n">
-        <v>42184.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18671.8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2585.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3085.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>75.84</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7056</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3537.07</v>
-      </c>
-      <c r="E7" t="n">
-        <v>382.86</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>63.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3569613.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>10092852</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8792638.369999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3383558.39</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>104573.7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>93707.33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>536500.8</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2320164</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1892013.09</v>
-      </c>
-      <c r="E6" t="n">
-        <v>476389.37</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>693.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>29068.24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>166844.7</v>
-      </c>
-      <c r="C7" t="n">
-        <v>388080</v>
-      </c>
-      <c r="D7" t="n">
-        <v>358411.51</v>
-      </c>
-      <c r="E7" t="n">
-        <v>70538.13</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3221.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5940</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>601.9400000000001</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>686.72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>63330</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>32</v>
@@ -576,7 +576,7 @@
         <v>40590</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>18</v>
@@ -614,7 +614,7 @@
         <v>6840</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -652,7 +652,7 @@
         <v>1140</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>5</v>
@@ -1546,7 +1546,7 @@
         <v>3570</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>2034.9</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>562955.08</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>10890</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>8</v>
@@ -9896,7 +9896,7 @@
         <v>11970</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -9972,7 +9972,7 @@
         <v>420</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -10828,7 +10828,7 @@
         <v>14612.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>5.4</v>
@@ -10866,7 +10866,7 @@
         <v>3898.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -10904,7 +10904,7 @@
         <v>832.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
@@ -11760,7 +11760,7 @@
         <v>4309.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -11836,7 +11836,7 @@
         <v>306.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="J7" t="n">
         <v>1.4</v>
@@ -12692,7 +12692,7 @@
         <v>1192140.18</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>
@@ -12768,7 +12768,7 @@
         <v>84820.89</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>81666.2</v>
@@ -13586,7 +13586,7 @@
         <v>3990</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -16420,7 +16420,7 @@
         <v>4042520.46</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>229998</v>
       </c>
       <c r="J5" t="n">
         <v>314998.2</v>
@@ -16458,7 +16458,7 @@
         <v>1078603.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>116666</v>
@@ -16496,7 +16496,7 @@
         <v>230228.13</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>210831.5</v>
       </c>
       <c r="J7" t="n">
         <v>204165.5</v>
@@ -17314,7 +17314,7 @@
         <v>6030</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -20110,7 +20110,7 @@
         <v>28410</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>966</v>
       </c>
       <c r="L4" t="n">
         <v>1310790</v>
@@ -582,7 +582,7 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="L5" t="n">
         <v>726840</v>
@@ -620,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
         <v>331890</v>
@@ -658,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L7" t="n">
         <v>167940</v>
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L8" t="n">
         <v>72600</v>
@@ -734,7 +734,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
         <v>27270</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>9510</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>570</v>
@@ -1476,7 +1476,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L4" t="n">
         <v>106920</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L5" t="n">
         <v>91500</v>
@@ -1552,7 +1552,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
         <v>44370</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
         <v>19290</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>8190</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>2040</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>21.42</v>
       </c>
       <c r="L5" t="n">
         <v>19215</v>
@@ -2484,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="L6" t="n">
         <v>16416.9</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="L7" t="n">
         <v>11574</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>5814.9</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>1652.4</v>
@@ -3378,7 +3378,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>456974.28</v>
       </c>
       <c r="L5" t="n">
         <v>181005.3</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>416013</v>
       </c>
       <c r="L6" t="n">
         <v>154647.2</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>157444.92</v>
       </c>
       <c r="L7" t="n">
         <v>109027.08</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>76802.39999999999</v>
       </c>
       <c r="L8" t="n">
         <v>54776.36</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L9" t="n">
         <v>15565.61</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>85980</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
         <v>25080</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>6360</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="L5" t="n">
         <v>5266.8</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>2353.2</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>107523.36</v>
       </c>
       <c r="L5" t="n">
         <v>49613.26</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>22167.14</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>27300</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>8190</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>1380</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="n">
         <v>1719.9</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>510.6</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>44801.4</v>
       </c>
       <c r="L5" t="n">
         <v>16201.46</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>4809.85</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>169.56</v>
@@ -9864,7 +9864,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L4" t="n">
         <v>286650</v>
@@ -9902,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="L5" t="n">
         <v>180240</v>
@@ -9940,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L6" t="n">
         <v>76770</v>
@@ -9978,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L7" t="n">
         <v>36030</v>
@@ -10016,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>10440</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>3570</v>
@@ -10834,7 +10834,7 @@
         <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>237.72</v>
       </c>
       <c r="L5" t="n">
         <v>152636.4</v>
@@ -10872,7 +10872,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>159.25</v>
       </c>
       <c r="L6" t="n">
         <v>122799.3</v>
@@ -10910,7 +10910,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>93.48</v>
       </c>
       <c r="L7" t="n">
         <v>100764</v>
@@ -10948,7 +10948,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>64.8</v>
       </c>
       <c r="L8" t="n">
         <v>51546</v>
@@ -10986,7 +10986,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L9" t="n">
         <v>22088.7</v>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>8463.9</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>570</v>
@@ -11766,7 +11766,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>73.08</v>
       </c>
       <c r="L5" t="n">
         <v>37850.4</v>
@@ -11804,7 +11804,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>48.75</v>
       </c>
       <c r="L6" t="n">
         <v>28404.9</v>
@@ -11842,7 +11842,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17.22</v>
       </c>
       <c r="L7" t="n">
         <v>21618</v>
@@ -11880,7 +11880,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L8" t="n">
         <v>7412.4</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>2891.7</v>
@@ -12698,7 +12698,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1559088.72</v>
       </c>
       <c r="L5" t="n">
         <v>356550.77</v>
@@ -12736,7 +12736,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1040032.5</v>
       </c>
       <c r="L6" t="n">
         <v>267574.16</v>
@@ -12774,7 +12774,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>367371.48</v>
       </c>
       <c r="L7" t="n">
         <v>203641.56</v>
@@ -12812,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>153604.8</v>
       </c>
       <c r="L8" t="n">
         <v>69824.81</v>
@@ -12850,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L9" t="n">
         <v>27239.81</v>
@@ -13592,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="L4" t="n">
         <v>177420</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>47370</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
         <v>9947.700000000001</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>134404.2</v>
       </c>
       <c r="L5" t="n">
         <v>93707.33</v>
@@ -16426,7 +16426,7 @@
         <v>314998.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5071518.48</v>
       </c>
       <c r="L5" t="n">
         <v>1437834.89</v>
@@ -16464,7 +16464,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3397439.5</v>
       </c>
       <c r="L6" t="n">
         <v>1156769.41</v>
@@ -16502,7 +16502,7 @@
         <v>204165.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1994302.32</v>
       </c>
       <c r="L7" t="n">
         <v>949196.88</v>
@@ -16540,7 +16540,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1382443.2</v>
       </c>
       <c r="L8" t="n">
         <v>485563.32</v>
@@ -16578,7 +16578,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L9" t="n">
         <v>208075.55</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L10" t="n">
         <v>79729.94</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L13" t="n">
         <v>5369.4</v>
@@ -17320,7 +17320,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="L4" t="n">
         <v>256140</v>
@@ -17358,7 +17358,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="L5" t="n">
         <v>202620</v>
@@ -17396,7 +17396,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
         <v>132180</v>
@@ -17434,7 +17434,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L7" t="n">
         <v>84420</v>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L8" t="n">
         <v>44040</v>
@@ -17510,7 +17510,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>18570</v>
@@ -17548,7 +17548,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>4170</v>
@@ -17662,7 +17662,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>240</v>
@@ -18290,7 +18290,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>42550.2</v>
@@ -18328,7 +18328,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>48906.6</v>
@@ -18366,7 +18366,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>66.42</v>
       </c>
       <c r="L7" t="n">
         <v>50652</v>
@@ -18404,7 +18404,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>53.1</v>
       </c>
       <c r="L8" t="n">
         <v>31268.4</v>
@@ -18442,7 +18442,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>15041.7</v>
@@ -18480,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>3711.3</v>
@@ -18594,7 +18594,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>240</v>
@@ -19222,7 +19222,7 @@
         <v>87499.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1836857.4</v>
       </c>
       <c r="L5" t="n">
         <v>400822.88</v>
@@ -19260,7 +19260,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1747254.6</v>
       </c>
       <c r="L6" t="n">
         <v>460700.17</v>
@@ -19298,7 +19298,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1417004.28</v>
       </c>
       <c r="L7" t="n">
         <v>477141.84</v>
@@ -19336,7 +19336,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1132835.4</v>
       </c>
       <c r="L8" t="n">
         <v>294548.33</v>
@@ -19374,7 +19374,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>448014</v>
       </c>
       <c r="L9" t="n">
         <v>141692.81</v>
@@ -19412,7 +19412,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>85336</v>
       </c>
       <c r="L10" t="n">
         <v>34960.45</v>
@@ -19526,7 +19526,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L13" t="n">
         <v>2260.8</v>
@@ -20116,7 +20116,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>216</v>
       </c>
       <c r="L4" t="n">
         <v>310890</v>
@@ -20154,7 +20154,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
         <v>116730</v>
@@ -20192,7 +20192,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L6" t="n">
         <v>26160</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>5160</v>
@@ -21086,7 +21086,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L5" t="n">
         <v>24513.3</v>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="L6" t="n">
         <v>9679.200000000001</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>3096</v>
@@ -22018,7 +22018,7 @@
         <v>104999.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>896028</v>
       </c>
       <c r="L5" t="n">
         <v>230915.29</v>
@@ -22056,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>124803.9</v>
       </c>
       <c r="L6" t="n">
         <v>91178.06</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>29164.32</v>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>157440.87</v>
+        <v>157350.69</v>
       </c>
       <c r="C4" t="n">
         <v>28166040</v>
@@ -532,7 +537,7 @@
         <v>124</v>
       </c>
       <c r="G4" t="n">
-        <v>486390</v>
+        <v>484140</v>
       </c>
       <c r="H4" t="n">
         <v>63330</v>
@@ -544,10 +549,13 @@
         <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="L4" t="n">
-        <v>1310790</v>
+        <v>1308150</v>
+      </c>
+      <c r="M4" t="n">
+        <v>62910</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>109720.62</v>
+        <v>109686.69</v>
       </c>
       <c r="C5" t="n">
         <v>13558608</v>
@@ -570,7 +578,7 @@
         <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>304830</v>
+        <v>303960</v>
       </c>
       <c r="H5" t="n">
         <v>40590</v>
@@ -582,10 +590,13 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="L5" t="n">
-        <v>726840</v>
+        <v>725310</v>
+      </c>
+      <c r="M5" t="n">
+        <v>33750</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>66841.83</v>
+        <v>66840.12</v>
       </c>
       <c r="C6" t="n">
         <v>5656392</v>
@@ -608,7 +619,7 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>163080</v>
+        <v>162450</v>
       </c>
       <c r="H6" t="n">
         <v>6840</v>
@@ -620,10 +631,13 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L6" t="n">
-        <v>331890</v>
+        <v>331110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14970</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>34573.68</v>
+        <v>34573.14</v>
       </c>
       <c r="C7" t="n">
         <v>2553768</v>
@@ -646,7 +660,7 @@
         <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>63930</v>
+        <v>63480</v>
       </c>
       <c r="H7" t="n">
         <v>1140</v>
@@ -661,7 +675,10 @@
         <v>114</v>
       </c>
       <c r="L7" t="n">
-        <v>167940</v>
+        <v>166920</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8970</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>19068.57</v>
+        <v>19068.48</v>
       </c>
       <c r="C8" t="n">
         <v>1045296</v>
@@ -684,7 +701,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>27930</v>
+        <v>27480</v>
       </c>
       <c r="H8" t="n">
         <v>180</v>
@@ -699,7 +716,10 @@
         <v>72</v>
       </c>
       <c r="L8" t="n">
-        <v>72600</v>
+        <v>71910</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4440</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +727,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>10756.8</v>
+        <v>10756.53</v>
       </c>
       <c r="C9" t="n">
         <v>352800</v>
@@ -722,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>18690</v>
+        <v>18360</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -737,7 +757,10 @@
         <v>26</v>
       </c>
       <c r="L9" t="n">
-        <v>27270</v>
+        <v>26910</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3150</v>
       </c>
     </row>
     <row r="10">
@@ -775,7 +798,10 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>9510</v>
+        <v>9420</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5490</v>
+        <v>5190</v>
+      </c>
+      <c r="M11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2310</v>
+        <v>2130</v>
+      </c>
+      <c r="M12" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>570</v>
       </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>870</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>390</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>330</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>570</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>90</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>35550</v>
+        <v>35670</v>
       </c>
       <c r="H4" t="n">
         <v>4980</v>
@@ -1479,7 +1556,10 @@
         <v>46</v>
       </c>
       <c r="L4" t="n">
-        <v>106920</v>
+        <v>107160</v>
+      </c>
+      <c r="M4" t="n">
+        <v>11130</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>7910.37</v>
+        <v>7910.28</v>
       </c>
       <c r="C5" t="n">
         <v>779688</v>
@@ -1517,7 +1597,10 @@
         <v>51</v>
       </c>
       <c r="L5" t="n">
-        <v>91500</v>
+        <v>91560</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10470</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1623,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>20970</v>
+        <v>21000</v>
       </c>
       <c r="H6" t="n">
         <v>3570</v>
@@ -1555,7 +1638,10 @@
         <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>44370</v>
+        <v>44400</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3210</v>
       </c>
     </row>
     <row r="7">
@@ -1593,7 +1679,10 @@
         <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>19290</v>
+        <v>19350</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2100</v>
       </c>
     </row>
     <row r="8">
@@ -1633,6 +1722,9 @@
       <c r="L8" t="n">
         <v>8190</v>
       </c>
+      <c r="M8" t="n">
+        <v>660</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1671,6 +1763,9 @@
       <c r="L9" t="n">
         <v>2040</v>
       </c>
+      <c r="M9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1804,9 @@
       <c r="L10" t="n">
         <v>1170</v>
       </c>
+      <c r="M10" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,7 +1843,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1785,6 +1886,9 @@
       <c r="L12" t="n">
         <v>810</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>120</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3559.67</v>
+        <v>3559.63</v>
       </c>
       <c r="C5" t="n">
         <v>428828.4</v>
@@ -2446,10 +2598,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21.42</v>
+        <v>16.88</v>
       </c>
       <c r="L5" t="n">
-        <v>19215</v>
+        <v>19227.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>209.4</v>
       </c>
     </row>
     <row r="6">
@@ -2472,22 +2627,25 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>1048.5</v>
+        <v>1050</v>
       </c>
       <c r="H6" t="n">
         <v>2034.9</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>19.5</v>
+        <v>15.21</v>
       </c>
       <c r="L6" t="n">
-        <v>16416.9</v>
+        <v>16428</v>
+      </c>
+      <c r="M6" t="n">
+        <v>256.8</v>
       </c>
     </row>
     <row r="7">
@@ -2522,10 +2680,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>7.38</v>
+        <v>5.74</v>
       </c>
       <c r="L7" t="n">
-        <v>11574</v>
+        <v>11610</v>
+      </c>
+      <c r="M7" t="n">
+        <v>735</v>
       </c>
     </row>
     <row r="8">
@@ -2560,10 +2721,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>5814.9</v>
+      </c>
+      <c r="M8" t="n">
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>1652.4</v>
+      </c>
+      <c r="M9" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -2641,6 +2808,9 @@
       <c r="L10" t="n">
         <v>1041.3</v>
       </c>
+      <c r="M10" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2677,7 +2847,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>750</v>
+        <v>780</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2717,6 +2890,9 @@
       <c r="L12" t="n">
         <v>810</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2755,6 +2931,9 @@
       <c r="L13" t="n">
         <v>120</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>7831266.3</v>
+        <v>7831177.2</v>
       </c>
       <c r="C5" t="n">
-        <v>23585562</v>
+        <v>18010792.8</v>
       </c>
       <c r="D5" t="n">
-        <v>20547147.38</v>
+        <v>38932717.82</v>
       </c>
       <c r="E5" t="n">
-        <v>4535797.19</v>
+        <v>8493541.199999999</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -3369,7 +3593,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>280855.08</v>
+        <v>5786640</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3378,10 +3602,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>456974.28</v>
+        <v>819673.84</v>
       </c>
       <c r="L5" t="n">
-        <v>181005.3</v>
+        <v>3460968</v>
+      </c>
+      <c r="M5" t="n">
+        <v>62820</v>
       </c>
     </row>
     <row r="6">
@@ -3392,34 +3619,37 @@
         <v>11682000</v>
       </c>
       <c r="C6" t="n">
-        <v>21729708</v>
+        <v>16593595.2</v>
       </c>
       <c r="D6" t="n">
-        <v>17719821.51</v>
+        <v>33575503.1</v>
       </c>
       <c r="E6" t="n">
-        <v>3390771.38</v>
+        <v>6349414.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>19397.25</v>
+        <v>56700</v>
       </c>
       <c r="H6" t="n">
-        <v>562955.08</v>
+        <v>11598930</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>416013</v>
+        <v>738536.76</v>
       </c>
       <c r="L6" t="n">
-        <v>154647.2</v>
+        <v>2957040</v>
+      </c>
+      <c r="M6" t="n">
+        <v>77040</v>
       </c>
     </row>
     <row r="7">
@@ -3430,22 +3660,22 @@
         <v>9194139.9</v>
       </c>
       <c r="C7" t="n">
-        <v>13665960</v>
+        <v>10435824</v>
       </c>
       <c r="D7" t="n">
-        <v>12621205.17</v>
+        <v>23914649.09</v>
       </c>
       <c r="E7" t="n">
-        <v>2327758.17</v>
+        <v>4358861.1</v>
       </c>
       <c r="F7" t="n">
         <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>20146.5</v>
+        <v>58806</v>
       </c>
       <c r="H7" t="n">
-        <v>60586.35</v>
+        <v>1248300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3454,10 +3684,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>157444.92</v>
+        <v>278808.55</v>
       </c>
       <c r="L7" t="n">
-        <v>109027.08</v>
+        <v>2089800</v>
+      </c>
+      <c r="M7" t="n">
+        <v>220500</v>
       </c>
     </row>
     <row r="8">
@@ -3468,22 +3701,22 @@
         <v>6187302</v>
       </c>
       <c r="C8" t="n">
-        <v>5017320</v>
+        <v>3831408</v>
       </c>
       <c r="D8" t="n">
-        <v>5345515.8</v>
+        <v>10128678.91</v>
       </c>
       <c r="E8" t="n">
-        <v>569445.3100000001</v>
+        <v>1066319.1</v>
       </c>
       <c r="F8" t="n">
         <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>90187.5</v>
+        <v>263250</v>
       </c>
       <c r="H8" t="n">
-        <v>21163.72</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3492,10 +3725,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>76802.39999999999</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>54776.36</v>
+        <v>1046682</v>
+      </c>
+      <c r="M8" t="n">
+        <v>118800</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>2356002</v>
       </c>
       <c r="C9" t="n">
-        <v>1081080</v>
+        <v>825552</v>
       </c>
       <c r="D9" t="n">
-        <v>1256647.24</v>
+        <v>2381094.14</v>
       </c>
       <c r="E9" t="n">
-        <v>88777.89</v>
+        <v>166241.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>22172.25</v>
+        <v>64719</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>64002</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>15565.61</v>
+        <v>297432</v>
+      </c>
+      <c r="M9" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>1146420</v>
       </c>
       <c r="C10" t="n">
-        <v>637560</v>
+        <v>486864</v>
       </c>
       <c r="D10" t="n">
-        <v>802934.87</v>
+        <v>1521400.32</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H10" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3571,7 +3810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9809.049999999999</v>
+        <v>187434</v>
+      </c>
+      <c r="M10" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,10 +3824,10 @@
         <v>661122</v>
       </c>
       <c r="C11" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D11" t="n">
-        <v>612914.97</v>
+        <v>1161350.78</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -3594,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -3609,7 +3851,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7065</v>
+        <v>140400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3620,10 +3865,10 @@
         <v>576774</v>
       </c>
       <c r="C12" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D12" t="n">
-        <v>297579.46</v>
+        <v>563853.3100000001</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3632,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3647,7 +3892,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7630.2</v>
+        <v>145800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -3658,10 +3906,10 @@
         <v>640134</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -3673,7 +3921,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3685,7 +3933,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1130.4</v>
+        <v>21600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>705870</v>
       </c>
       <c r="C14" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D14" t="n">
-        <v>156012.53</v>
+        <v>295612.42</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3723,6 +3974,9 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3734,10 +3988,10 @@
         <v>276012</v>
       </c>
       <c r="C15" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D15" t="n">
-        <v>79129.81</v>
+        <v>149935.1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3761,6 +4015,9 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3772,10 +4029,10 @@
         <v>212058</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,6 +4056,9 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3839,6 +4099,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>26280</v>
+        <v>26340</v>
       </c>
       <c r="H4" t="n">
         <v>1560</v>
@@ -4275,7 +4568,10 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>85980</v>
+        <v>86520</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4313,7 +4609,10 @@
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>25080</v>
+        <v>25260</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>6360</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1260</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>210</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5.04</v>
+        <v>3.97</v>
       </c>
       <c r="L5" t="n">
-        <v>5266.8</v>
+        <v>5304.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>2353.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>756</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>149.1</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>1811313.9</v>
       </c>
       <c r="C5" t="n">
-        <v>9162846</v>
+        <v>6997082.4</v>
       </c>
       <c r="D5" t="n">
-        <v>7982440.58</v>
+        <v>15125121.79</v>
       </c>
       <c r="E5" t="n">
-        <v>2121582.56</v>
+        <v>3972785.4</v>
       </c>
       <c r="F5" t="n">
         <v>833.34</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>44817.3</v>
+        <v>923400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>107523.36</v>
+        <v>192864.43</v>
       </c>
       <c r="L5" t="n">
-        <v>49613.26</v>
+        <v>954828</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>183902.4</v>
       </c>
       <c r="C6" t="n">
-        <v>3966732</v>
+        <v>3029140.8</v>
       </c>
       <c r="D6" t="n">
-        <v>3234732.05</v>
+        <v>6129167.62</v>
       </c>
       <c r="E6" t="n">
-        <v>1345099.39</v>
+        <v>2518776</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1332</v>
+        <v>3888</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13867.1</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>22167.14</v>
+        <v>423576</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>59251.5</v>
       </c>
       <c r="C7" t="n">
-        <v>304920</v>
+        <v>232848</v>
       </c>
       <c r="D7" t="n">
-        <v>281609.04</v>
+        <v>533592.58</v>
       </c>
       <c r="E7" t="n">
-        <v>35269.06</v>
+        <v>66043.35000000001</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>582.75</v>
+        <v>1701</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7121.52</v>
+        <v>136080</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>34056</v>
       </c>
       <c r="C8" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D8" t="n">
-        <v>59066.47</v>
+        <v>111919.1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2164.5</v>
+        <v>6318</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1404.52</v>
+        <v>26838</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,13 +6754,13 @@
         <v>19008</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>24060</v>
+        <v>24120</v>
       </c>
       <c r="H4" t="n">
         <v>3210</v>
@@ -7071,7 +7580,10 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>27300</v>
+        <v>27330</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>8190</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>1380</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>30</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="L5" t="n">
         <v>1719.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>510.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>1196256.6</v>
       </c>
       <c r="C5" t="n">
-        <v>3567564</v>
+        <v>2724321.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3107971.87</v>
+        <v>5888982.53</v>
       </c>
       <c r="E5" t="n">
-        <v>91447.52</v>
+        <v>171240.75</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>191220.48</v>
+        <v>3939840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>44801.4</v>
+        <v>80360.17999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>16201.46</v>
+        <v>309582</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>403128</v>
       </c>
       <c r="C6" t="n">
-        <v>1372140</v>
+        <v>1047816</v>
       </c>
       <c r="D6" t="n">
-        <v>1118932.47</v>
+        <v>2120152.32</v>
       </c>
       <c r="E6" t="n">
-        <v>112091.62</v>
+        <v>209898</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1637.25</v>
+        <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27734.2</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>4809.85</v>
+        <v>91908</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,10 +9684,10 @@
         <v>75992.39999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D7" t="n">
-        <v>102403.29</v>
+        <v>194033.66</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -9034,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1165.5</v>
+        <v>3402</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34987.76</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>169.56</v>
+        <v>3240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>13068</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>17</v>
       </c>
       <c r="G4" t="n">
-        <v>111720</v>
+        <v>111780</v>
       </c>
       <c r="H4" t="n">
-        <v>10890</v>
+        <v>10770</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -9867,7 +10592,10 @@
         <v>300</v>
       </c>
       <c r="L4" t="n">
-        <v>286650</v>
+        <v>286830</v>
+      </c>
+      <c r="M4" t="n">
+        <v>18420</v>
       </c>
     </row>
     <row r="5">
@@ -9890,7 +10618,7 @@
         <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>80970</v>
+        <v>81000</v>
       </c>
       <c r="H5" t="n">
         <v>11970</v>
@@ -9905,7 +10633,10 @@
         <v>174</v>
       </c>
       <c r="L5" t="n">
-        <v>180240</v>
+        <v>180360</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11700</v>
       </c>
     </row>
     <row r="6">
@@ -9928,7 +10659,7 @@
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>42390</v>
+        <v>42510</v>
       </c>
       <c r="H6" t="n">
         <v>1380</v>
@@ -9940,10 +10671,13 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L6" t="n">
-        <v>76770</v>
+        <v>76800</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4590</v>
       </c>
     </row>
     <row r="7">
@@ -9983,6 +10717,9 @@
       <c r="L7" t="n">
         <v>36030</v>
       </c>
+      <c r="M7" t="n">
+        <v>2430</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>10440</v>
       </c>
+      <c r="M8" t="n">
+        <v>1170</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>3570</v>
       </c>
+      <c r="M9" t="n">
+        <v>570</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>2970</v>
       </c>
+      <c r="M10" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>2340</v>
       </c>
+      <c r="M11" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>720</v>
       </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>60</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>240</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>300</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>570</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>90</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>49374.28</v>
+        <v>49359.01</v>
       </c>
       <c r="C5" t="n">
         <v>7457234.4</v>
@@ -10828,16 +11628,19 @@
         <v>14612.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="J5" t="n">
         <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>237.72</v>
+        <v>184.37</v>
       </c>
       <c r="L5" t="n">
-        <v>152636.4</v>
+        <v>152315.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>675</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>53473.46</v>
+        <v>53472.1</v>
       </c>
       <c r="C6" t="n">
         <v>5090752.8</v>
@@ -10860,22 +11663,25 @@
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8154</v>
+        <v>8122.5</v>
       </c>
       <c r="H6" t="n">
         <v>3898.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>159.25</v>
+        <v>123.71</v>
       </c>
       <c r="L6" t="n">
-        <v>122799.3</v>
+        <v>122510.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1197.6</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>32845</v>
+        <v>32844.48</v>
       </c>
       <c r="C7" t="n">
         <v>2553768</v>
@@ -10898,22 +11704,25 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>9589.5</v>
+        <v>9522</v>
       </c>
       <c r="H7" t="n">
         <v>832.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>93.48</v>
+        <v>72.73</v>
       </c>
       <c r="L7" t="n">
-        <v>100764</v>
+        <v>100152</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3139.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>19068.57</v>
+        <v>19068.48</v>
       </c>
       <c r="C8" t="n">
         <v>1045296</v>
@@ -10936,7 +11745,7 @@
         <v>5.7</v>
       </c>
       <c r="G8" t="n">
-        <v>18154.5</v>
+        <v>17862</v>
       </c>
       <c r="H8" t="n">
         <v>153</v>
@@ -10948,10 +11757,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>64.8</v>
+        <v>52.99</v>
       </c>
       <c r="L8" t="n">
-        <v>51546</v>
+        <v>51056.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2664</v>
       </c>
     </row>
     <row r="9">
@@ -10959,7 +11771,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>10756.8</v>
+        <v>10756.53</v>
       </c>
       <c r="C9" t="n">
         <v>352800</v>
@@ -10974,7 +11786,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>15886.5</v>
+        <v>15606</v>
       </c>
       <c r="H9" t="n">
         <v>90</v>
@@ -10986,10 +11798,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>20.88</v>
       </c>
       <c r="L9" t="n">
-        <v>22088.7</v>
+        <v>21797.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3150</v>
       </c>
     </row>
     <row r="10">
@@ -11024,10 +11839,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>8463.9</v>
+        <v>8383.799999999999</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1200</v>
       </c>
     </row>
     <row r="11">
@@ -11065,7 +11883,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5490</v>
+        <v>5190</v>
+      </c>
+      <c r="M11" t="n">
+        <v>240</v>
       </c>
     </row>
     <row r="12">
@@ -11103,7 +11924,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2310</v>
+        <v>2130</v>
+      </c>
+      <c r="M12" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -11138,10 +11962,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>570</v>
+      </c>
+      <c r="M13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>870</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11219,6 +12049,9 @@
       <c r="L15" t="n">
         <v>390</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>330</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>570</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>90</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11760,16 +12632,19 @@
         <v>4309.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.32</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>73.08</v>
+        <v>57.59</v>
       </c>
       <c r="L5" t="n">
-        <v>37850.4</v>
+        <v>37875.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="6">
@@ -11792,7 +12667,7 @@
         <v>0.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2119.5</v>
+        <v>2125.5</v>
       </c>
       <c r="H6" t="n">
         <v>786.6</v>
@@ -11804,10 +12679,13 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>48.75</v>
+        <v>38.53</v>
       </c>
       <c r="L6" t="n">
-        <v>28404.9</v>
+        <v>28416</v>
+      </c>
+      <c r="M6" t="n">
+        <v>367.2</v>
       </c>
     </row>
     <row r="7">
@@ -11836,16 +12714,19 @@
         <v>306.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0.55</v>
+        <v>0.64</v>
       </c>
       <c r="J7" t="n">
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>17.22</v>
+        <v>13.4</v>
       </c>
       <c r="L7" t="n">
         <v>21618</v>
+      </c>
+      <c r="M7" t="n">
+        <v>850.5</v>
       </c>
     </row>
     <row r="8">
@@ -11880,10 +12761,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>7.2</v>
+        <v>5.89</v>
       </c>
       <c r="L8" t="n">
         <v>7412.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>702</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
         <v>2891.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>570</v>
       </c>
     </row>
     <row r="10">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>2643.3</v>
       </c>
+      <c r="M10" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>2340</v>
       </c>
+      <c r="M11" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>720</v>
       </c>
+      <c r="M12" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>60</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>240</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>300</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>300</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>570</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>90</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>37011872.7</v>
       </c>
       <c r="C5" t="n">
-        <v>108383814</v>
+        <v>82765821.59999999</v>
       </c>
       <c r="D5" t="n">
-        <v>94421248.05</v>
+        <v>178909302.53</v>
       </c>
       <c r="E5" t="n">
-        <v>10589623.28</v>
+        <v>19829678.85</v>
       </c>
       <c r="F5" t="n">
         <v>5833.38</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1192140.18</v>
+        <v>24562440</v>
       </c>
       <c r="I5" t="n">
-        <v>229998</v>
+        <v>257152.58</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1559088.72</v>
+        <v>2796534.26</v>
       </c>
       <c r="L5" t="n">
-        <v>356550.77</v>
+        <v>6817608</v>
+      </c>
+      <c r="M5" t="n">
+        <v>70200</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>40583030.4</v>
       </c>
       <c r="C6" t="n">
-        <v>68357520</v>
+        <v>52200288</v>
       </c>
       <c r="D6" t="n">
-        <v>55743181.32</v>
+        <v>105622133.76</v>
       </c>
       <c r="E6" t="n">
-        <v>2970427.82</v>
+        <v>5562297</v>
       </c>
       <c r="F6" t="n">
         <v>8333.4</v>
       </c>
       <c r="G6" t="n">
-        <v>39210.75</v>
+        <v>114777</v>
       </c>
       <c r="H6" t="n">
-        <v>217612.89</v>
+        <v>4483620</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1040032.5</v>
+        <v>1870959.79</v>
       </c>
       <c r="L6" t="n">
-        <v>267574.16</v>
+        <v>5114880</v>
+      </c>
+      <c r="M6" t="n">
+        <v>110160</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>13588532.1</v>
       </c>
       <c r="C7" t="n">
-        <v>26139960</v>
+        <v>19961424</v>
       </c>
       <c r="D7" t="n">
-        <v>24141575</v>
+        <v>45743436.29</v>
       </c>
       <c r="E7" t="n">
-        <v>775919.39</v>
+        <v>1452953.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>28887.75</v>
+        <v>84321</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>1747620</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>367371.48</v>
+        <v>650553.29</v>
       </c>
       <c r="L7" t="n">
-        <v>203641.56</v>
+        <v>3891240</v>
+      </c>
+      <c r="M7" t="n">
+        <v>255150</v>
       </c>
     </row>
     <row r="8">
@@ -12788,19 +13741,19 @@
         <v>2538162</v>
       </c>
       <c r="C8" t="n">
-        <v>5738040</v>
+        <v>4381776</v>
       </c>
       <c r="D8" t="n">
-        <v>6113379.95</v>
+        <v>11583627.26</v>
       </c>
       <c r="E8" t="n">
-        <v>81349.33</v>
+        <v>152331.3</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18759</v>
+        <v>54756</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12812,10 +13765,13 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>153604.8</v>
+        <v>285897.73</v>
       </c>
       <c r="L8" t="n">
-        <v>69824.81</v>
+        <v>1334232</v>
+      </c>
+      <c r="M8" t="n">
+        <v>210600</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>508860</v>
       </c>
       <c r="C9" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D9" t="n">
-        <v>1031095.17</v>
+        <v>1953718.27</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7548</v>
+        <v>22032</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12850,10 +13806,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21334</v>
+        <v>38990.47</v>
       </c>
       <c r="L9" t="n">
-        <v>27239.81</v>
+        <v>520506</v>
+      </c>
+      <c r="M9" t="n">
+        <v>171000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,22 +13823,22 @@
         <v>399366</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>264591.36</v>
       </c>
       <c r="E10" t="n">
-        <v>48086.64</v>
+        <v>90045</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24899.89</v>
+        <v>475794</v>
+      </c>
+      <c r="M10" t="n">
+        <v>63000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>128898</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>204944.26</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,7 +13876,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>22042.8</v>
+        <v>421200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,10 +13905,10 @@
         <v>53460</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>281926.66</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -12952,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3330</v>
+        <v>9720</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6782.4</v>
+        <v>129600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>31284</v>
       </c>
       <c r="C13" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D13" t="n">
-        <v>152401.13</v>
+        <v>288769.54</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13016,10 +13987,10 @@
         <v>15048</v>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D14" t="n">
-        <v>117009.4</v>
+        <v>221709.31</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -13028,7 +13999,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>8118</v>
       </c>
       <c r="C15" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D15" t="n">
-        <v>39564.91</v>
+        <v>74967.55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>990</v>
       </c>
       <c r="C16" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D16" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13157,7 +14137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5369.4</v>
+        <v>102600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D18" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13180,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>67155</v>
+        <v>196020</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13195,7 +14178,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D19" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D20" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D24" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>50160</v>
+        <v>50220</v>
       </c>
       <c r="H4" t="n">
         <v>3990</v>
@@ -13595,7 +14608,10 @@
         <v>62</v>
       </c>
       <c r="L4" t="n">
-        <v>177420</v>
+        <v>179490</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13633,7 +14649,10 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>47370</v>
+        <v>46950</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="H6" t="n">
         <v>210</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8340</v>
+        <v>8760</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>570</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>90</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>90</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>9947.700000000001</v>
+        <v>9859.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>37.5</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
         <v>119.7</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3085.8</v>
+        <v>3241.2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>342</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>63.9</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>3569613.3</v>
       </c>
       <c r="C5" t="n">
-        <v>10092852</v>
+        <v>7707268.8</v>
       </c>
       <c r="D5" t="n">
-        <v>8792638.369999999</v>
+        <v>16660283.9</v>
       </c>
       <c r="E5" t="n">
-        <v>3383558.39</v>
+        <v>6335907.75</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>104573.7</v>
+        <v>2154600</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>134404.2</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>93707.33</v>
+        <v>1774710</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>536500.8</v>
       </c>
       <c r="C6" t="n">
-        <v>2320164</v>
+        <v>1771761.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1892013.09</v>
+        <v>3584984.83</v>
       </c>
       <c r="E6" t="n">
-        <v>476389.37</v>
+        <v>892066.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>693.75</v>
+        <v>2268</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>682290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>29068.24</v>
+        <v>583416</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>166844.7</v>
       </c>
       <c r="C7" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D7" t="n">
-        <v>358411.51</v>
+        <v>679117.8199999999</v>
       </c>
       <c r="E7" t="n">
-        <v>70538.13</v>
+        <v>132086.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3221.64</v>
+        <v>61560</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>601.9400000000001</v>
+        <v>11502</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>686.72</v>
+        <v>13122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>108623413.8</v>
+        <v>108589823.1</v>
       </c>
       <c r="C5" t="n">
-        <v>410147892</v>
+        <v>313203844.8</v>
       </c>
       <c r="D5" t="n">
-        <v>357310509.91</v>
+        <v>677031657.98</v>
       </c>
       <c r="E5" t="n">
-        <v>52655484.32</v>
+        <v>98600423.84999999</v>
       </c>
       <c r="F5" t="n">
         <v>44167.02</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4042520.46</v>
+        <v>83290680</v>
       </c>
       <c r="I5" t="n">
-        <v>229998</v>
+        <v>257152.58</v>
       </c>
       <c r="J5" t="n">
-        <v>314998.2</v>
+        <v>131101.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5071518.48</v>
+        <v>8952124.050000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1437834.89</v>
+        <v>27416718</v>
+      </c>
+      <c r="M5" t="n">
+        <v>202500</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>117641620.8</v>
+        <v>117638611.2</v>
       </c>
       <c r="C6" t="n">
-        <v>279991404</v>
+        <v>213811617.6</v>
       </c>
       <c r="D6" t="n">
-        <v>228323256.93</v>
+        <v>432626717.95</v>
       </c>
       <c r="E6" t="n">
-        <v>31805996.04</v>
+        <v>59558557.5</v>
       </c>
       <c r="F6" t="n">
         <v>133334.4</v>
       </c>
       <c r="G6" t="n">
-        <v>150849</v>
+        <v>438615</v>
       </c>
       <c r="H6" t="n">
-        <v>1078603.02</v>
+        <v>22223160</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>3397439.5</v>
+        <v>6006765.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1156769.41</v>
+        <v>22051926</v>
+      </c>
+      <c r="M6" t="n">
+        <v>359280</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>72258991.2</v>
+        <v>72257862.59999999</v>
       </c>
       <c r="C7" t="n">
-        <v>140457240</v>
+        <v>107258256</v>
       </c>
       <c r="D7" t="n">
-        <v>129719364.26</v>
+        <v>245792143.87</v>
       </c>
       <c r="E7" t="n">
-        <v>21337783.24</v>
+        <v>39956226.75</v>
       </c>
       <c r="F7" t="n">
         <v>625005</v>
       </c>
       <c r="G7" t="n">
-        <v>177405.75</v>
+        <v>514188</v>
       </c>
       <c r="H7" t="n">
-        <v>230228.13</v>
+        <v>4743540</v>
       </c>
       <c r="I7" t="n">
-        <v>210831.5</v>
+        <v>123914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>204165.5</v>
+        <v>84973</v>
       </c>
       <c r="K7" t="n">
-        <v>1994302.32</v>
+        <v>3531574.99</v>
       </c>
       <c r="L7" t="n">
-        <v>949196.88</v>
+        <v>18027360</v>
+      </c>
+      <c r="M7" t="n">
+        <v>941850</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>41950854</v>
+        <v>41950656</v>
       </c>
       <c r="C8" t="n">
-        <v>57491280</v>
+        <v>43902432</v>
       </c>
       <c r="D8" t="n">
-        <v>61251932.46</v>
+        <v>116060110.85</v>
       </c>
       <c r="E8" t="n">
-        <v>9273823.57</v>
+        <v>17365768.2</v>
       </c>
       <c r="F8" t="n">
         <v>237501.9</v>
       </c>
       <c r="G8" t="n">
-        <v>335858.25</v>
+        <v>964548</v>
       </c>
       <c r="H8" t="n">
-        <v>42327.45</v>
+        <v>872100</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1382443.2</v>
+        <v>2573079.55</v>
       </c>
       <c r="L8" t="n">
-        <v>485563.32</v>
+        <v>9190098</v>
+      </c>
+      <c r="M8" t="n">
+        <v>799200</v>
       </c>
     </row>
     <row r="9">
@@ -16551,37 +17795,40 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>23664960</v>
+        <v>23664366</v>
       </c>
       <c r="C9" t="n">
-        <v>19404000</v>
+        <v>14817600</v>
       </c>
       <c r="D9" t="n">
-        <v>22555206.83</v>
+        <v>42737587.2</v>
       </c>
       <c r="E9" t="n">
-        <v>2397002.93</v>
+        <v>4488525.9</v>
       </c>
       <c r="F9" t="n">
         <v>41667</v>
       </c>
       <c r="G9" t="n">
-        <v>293900.25</v>
+        <v>842724</v>
       </c>
       <c r="H9" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>554684</v>
+        <v>1013752.17</v>
       </c>
       <c r="L9" t="n">
-        <v>208075.55</v>
+        <v>3923478</v>
+      </c>
+      <c r="M9" t="n">
+        <v>945000</v>
       </c>
     </row>
     <row r="10">
@@ -16592,22 +17839,22 @@
         <v>11225214</v>
       </c>
       <c r="C10" t="n">
-        <v>3437280</v>
+        <v>2624832</v>
       </c>
       <c r="D10" t="n">
-        <v>4328866.24</v>
+        <v>8202332.16</v>
       </c>
       <c r="E10" t="n">
-        <v>240433.2</v>
+        <v>450225</v>
       </c>
       <c r="F10" t="n">
         <v>83334</v>
       </c>
       <c r="G10" t="n">
-        <v>112665</v>
+        <v>328860</v>
       </c>
       <c r="H10" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16616,10 +17863,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>85336</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>79729.94</v>
+        <v>1509084</v>
+      </c>
+      <c r="M10" t="n">
+        <v>360000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,19 +17880,19 @@
         <v>4578354</v>
       </c>
       <c r="C11" t="n">
-        <v>1829520</v>
+        <v>1397088</v>
       </c>
       <c r="D11" t="n">
-        <v>2379552.25</v>
+        <v>4508773.63</v>
       </c>
       <c r="E11" t="n">
-        <v>271805.59</v>
+        <v>508971.6</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>36075</v>
+        <v>105300</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -16657,7 +17907,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>51715.8</v>
+        <v>934200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,19 +17921,19 @@
         <v>2657160</v>
       </c>
       <c r="C12" t="n">
-        <v>859320</v>
+        <v>656208</v>
       </c>
       <c r="D12" t="n">
-        <v>1153120.4</v>
+        <v>2184931.58</v>
       </c>
       <c r="E12" t="n">
-        <v>158520.1</v>
+        <v>296838</v>
       </c>
       <c r="F12" t="n">
         <v>41667</v>
       </c>
       <c r="G12" t="n">
-        <v>14985</v>
+        <v>43740</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -16695,7 +17948,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>21760.2</v>
+        <v>383400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,10 +17962,10 @@
         <v>2282544</v>
       </c>
       <c r="C13" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D13" t="n">
-        <v>723905.37</v>
+        <v>1371655.3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16718,10 +17974,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>8880</v>
+        <v>25920</v>
       </c>
       <c r="H13" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16730,10 +17986,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21334</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>5369.4</v>
+        <v>102600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,10 +18003,10 @@
         <v>2185920</v>
       </c>
       <c r="C14" t="n">
-        <v>332640</v>
+        <v>254016</v>
       </c>
       <c r="D14" t="n">
-        <v>468037.6</v>
+        <v>886837.25</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16756,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>10545</v>
+        <v>30780</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8195.4</v>
+        <v>156600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>1084644</v>
       </c>
       <c r="C15" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D15" t="n">
-        <v>276954.35</v>
+        <v>524772.86</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16794,7 +18056,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -16809,7 +18071,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3673.8</v>
+        <v>70200</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>370260</v>
       </c>
       <c r="C16" t="n">
-        <v>138600</v>
+        <v>105840</v>
       </c>
       <c r="D16" t="n">
-        <v>200633.4</v>
+        <v>380160</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -16847,7 +18112,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3108.6</v>
+        <v>59400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16870,7 +18138,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -16885,7 +18153,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5369.4</v>
+        <v>102600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>6732</v>
       </c>
       <c r="C18" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D18" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16908,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>67155</v>
+        <v>196020</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16923,7 +18194,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>396</v>
       </c>
       <c r="C19" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D19" t="n">
-        <v>120380.04</v>
+        <v>228096</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16961,6 +18235,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16972,10 +18249,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16999,6 +18276,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17039,6 +18319,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>31943.16</v>
+        <v>31862.88</v>
       </c>
       <c r="C4" t="n">
         <v>5132736</v>
@@ -17308,7 +18609,7 @@
         <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>100860</v>
+        <v>98430</v>
       </c>
       <c r="H4" t="n">
         <v>6030</v>
@@ -17320,10 +18621,13 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="L4" t="n">
-        <v>256140</v>
+        <v>253590</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26190</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>35592.21</v>
+        <v>35568.36</v>
       </c>
       <c r="C5" t="n">
         <v>3640392</v>
@@ -17346,7 +18650,7 @@
         <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>87600</v>
+        <v>86820</v>
       </c>
       <c r="H5" t="n">
         <v>1440</v>
@@ -17358,10 +18662,13 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="L5" t="n">
-        <v>202620</v>
+        <v>201210</v>
+      </c>
+      <c r="M5" t="n">
+        <v>7470</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>25571.43</v>
+        <v>25569.72</v>
       </c>
       <c r="C6" t="n">
         <v>2459016</v>
@@ -17384,7 +18691,7 @@
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>70980</v>
+        <v>70290</v>
       </c>
       <c r="H6" t="n">
         <v>60</v>
@@ -17396,10 +18703,13 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L6" t="n">
-        <v>132180</v>
+        <v>131430</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4770</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>17207.82</v>
+        <v>17207.28</v>
       </c>
       <c r="C7" t="n">
         <v>1400616</v>
@@ -17422,7 +18732,7 @@
         <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>36300</v>
+        <v>35910</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -17437,7 +18747,10 @@
         <v>81</v>
       </c>
       <c r="L7" t="n">
-        <v>84420</v>
+        <v>83400</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2850</v>
       </c>
     </row>
     <row r="8">
@@ -17460,7 +18773,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>14580</v>
+        <v>14130</v>
       </c>
       <c r="H8" t="n">
         <v>30</v>
@@ -17475,7 +18788,10 @@
         <v>59</v>
       </c>
       <c r="L8" t="n">
-        <v>44040</v>
+        <v>43350</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1890</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>15600</v>
+        <v>15270</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17513,7 +18829,10 @@
         <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>18570</v>
+        <v>18210</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2370</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>4170</v>
+        <v>4080</v>
+      </c>
+      <c r="M10" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1920</v>
+        <v>1620</v>
+      </c>
+      <c r="M11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>690</v>
+        <v>510</v>
+      </c>
+      <c r="M12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>240</v>
       </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>90</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>90</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>30</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>16016.49</v>
+        <v>16005.76</v>
       </c>
       <c r="C5" t="n">
         <v>2002215.6</v>
@@ -18290,10 +19666,13 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>86.09999999999999</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>42550.2</v>
+        <v>42254.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>149.4</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>20457.14</v>
+        <v>20455.78</v>
       </c>
       <c r="C6" t="n">
         <v>2213114.4</v>
@@ -18316,7 +19695,7 @@
         <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>3549</v>
+        <v>3514.5</v>
       </c>
       <c r="H6" t="n">
         <v>34.2</v>
@@ -18328,10 +19707,13 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>81.90000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="L6" t="n">
-        <v>48906.6</v>
+        <v>48629.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>381.6</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>16347.43</v>
+        <v>16346.92</v>
       </c>
       <c r="C7" t="n">
         <v>1400616</v>
@@ -18354,7 +19736,7 @@
         <v>12.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5445</v>
+        <v>5386.5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -18366,10 +19748,13 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>66.42</v>
+        <v>51.68</v>
       </c>
       <c r="L7" t="n">
-        <v>50652</v>
+        <v>50040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>997.5</v>
       </c>
     </row>
     <row r="8">
@@ -18392,7 +19777,7 @@
         <v>2.85</v>
       </c>
       <c r="G8" t="n">
-        <v>9477</v>
+        <v>9184.5</v>
       </c>
       <c r="H8" t="n">
         <v>25.5</v>
@@ -18404,10 +19789,13 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>53.1</v>
+        <v>43.42</v>
       </c>
       <c r="L8" t="n">
-        <v>31268.4</v>
+        <v>30778.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1134</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13260</v>
+        <v>12979.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>16.86</v>
       </c>
       <c r="L9" t="n">
-        <v>15041.7</v>
+        <v>14750.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2370</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>3711.3</v>
+        <v>3631.2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>510</v>
       </c>
     </row>
     <row r="11">
@@ -18521,7 +19915,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1920</v>
+        <v>1620</v>
+      </c>
+      <c r="M11" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -18559,7 +19956,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>690</v>
+        <v>510</v>
+      </c>
+      <c r="M12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -18594,10 +19994,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>240</v>
+      </c>
+      <c r="M13" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>90</v>
       </c>
+      <c r="M14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18675,6 +20081,9 @@
       <c r="L15" t="n">
         <v>90</v>
       </c>
+      <c r="M15" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>30</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>35236287.9</v>
+        <v>35212676.4</v>
       </c>
       <c r="C5" t="n">
-        <v>110121858</v>
+        <v>84093055.2</v>
       </c>
       <c r="D5" t="n">
-        <v>95935388.19</v>
+        <v>181778294.02</v>
       </c>
       <c r="E5" t="n">
-        <v>19606349.15</v>
+        <v>36714016.8</v>
       </c>
       <c r="F5" t="n">
         <v>7500.06</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>143415.36</v>
+        <v>2954880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>1836857.4</v>
+        <v>3166191.09</v>
       </c>
       <c r="L5" t="n">
-        <v>400822.88</v>
+        <v>7605738</v>
+      </c>
+      <c r="M5" t="n">
+        <v>44820</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>45005716.8</v>
+        <v>45002707.2</v>
       </c>
       <c r="C6" t="n">
-        <v>121721292</v>
+        <v>92950804.8</v>
       </c>
       <c r="D6" t="n">
-        <v>99259482.36</v>
+        <v>188076784.9</v>
       </c>
       <c r="E6" t="n">
-        <v>18495116.64</v>
+        <v>34633170</v>
       </c>
       <c r="F6" t="n">
         <v>58333.8</v>
       </c>
       <c r="G6" t="n">
-        <v>65656.5</v>
+        <v>189783</v>
       </c>
       <c r="H6" t="n">
-        <v>9461.43</v>
+        <v>194940</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1747254.6</v>
+        <v>3077236.5</v>
       </c>
       <c r="L6" t="n">
-        <v>460700.17</v>
+        <v>8753238</v>
+      </c>
+      <c r="M6" t="n">
+        <v>114480</v>
       </c>
     </row>
     <row r="7">
@@ -19271,22 +20725,22 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>35964343.8</v>
+        <v>35963215.2</v>
       </c>
       <c r="C7" t="n">
-        <v>77033880</v>
+        <v>58825872</v>
       </c>
       <c r="D7" t="n">
-        <v>71144683.89</v>
+        <v>134804888.06</v>
       </c>
       <c r="E7" t="n">
-        <v>16117961.88</v>
+        <v>30181810.95</v>
       </c>
       <c r="F7" t="n">
         <v>525004.2</v>
       </c>
       <c r="G7" t="n">
-        <v>100732.5</v>
+        <v>290871</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -19295,13 +20749,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>1417004.28</v>
+        <v>2509276.97</v>
       </c>
       <c r="L7" t="n">
-        <v>477141.84</v>
+        <v>9007200</v>
+      </c>
+      <c r="M7" t="n">
+        <v>299250</v>
       </c>
     </row>
     <row r="8">
@@ -19312,34 +20769,37 @@
         <v>24650208</v>
       </c>
       <c r="C8" t="n">
-        <v>39722760</v>
+        <v>30333744</v>
       </c>
       <c r="D8" t="n">
-        <v>42321127.88</v>
+        <v>80190038.02</v>
       </c>
       <c r="E8" t="n">
-        <v>8175607.62</v>
+        <v>15309295.65</v>
       </c>
       <c r="F8" t="n">
         <v>118750.95</v>
       </c>
       <c r="G8" t="n">
-        <v>175324.5</v>
+        <v>495963</v>
       </c>
       <c r="H8" t="n">
-        <v>7054.58</v>
+        <v>145350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1132835.4</v>
+        <v>2108495.74</v>
       </c>
       <c r="L8" t="n">
-        <v>294548.33</v>
+        <v>5540130</v>
+      </c>
+      <c r="M8" t="n">
+        <v>340200</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>15625962</v>
       </c>
       <c r="C9" t="n">
-        <v>14663880</v>
+        <v>11197872</v>
       </c>
       <c r="D9" t="n">
-        <v>17045292.02</v>
+        <v>32297405.18</v>
       </c>
       <c r="E9" t="n">
-        <v>1864335.61</v>
+        <v>3491075.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>245310</v>
+        <v>700893</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19371,13 +20831,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>448014</v>
+        <v>818799.83</v>
       </c>
       <c r="L9" t="n">
-        <v>141692.81</v>
+        <v>2655018</v>
+      </c>
+      <c r="M9" t="n">
+        <v>711000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,19 +20851,19 @@
         <v>6879906</v>
       </c>
       <c r="C10" t="n">
-        <v>2245320</v>
+        <v>1714608</v>
       </c>
       <c r="D10" t="n">
-        <v>2827727.14</v>
+        <v>5357975.04</v>
       </c>
       <c r="E10" t="n">
-        <v>144259.92</v>
+        <v>270135</v>
       </c>
       <c r="F10" t="n">
         <v>83334</v>
       </c>
       <c r="G10" t="n">
-        <v>89355</v>
+        <v>260820</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -19412,10 +20875,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>85336</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>34960.45</v>
+        <v>653616</v>
+      </c>
+      <c r="M10" t="n">
+        <v>153000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,19 +20892,19 @@
         <v>2152062</v>
       </c>
       <c r="C11" t="n">
-        <v>859320</v>
+        <v>656208</v>
       </c>
       <c r="D11" t="n">
-        <v>1117668.48</v>
+        <v>2117757.31</v>
       </c>
       <c r="E11" t="n">
-        <v>203854.19</v>
+        <v>381728.7</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>27750</v>
+        <v>81000</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -19453,7 +20919,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>18086.4</v>
+        <v>291600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>806454</v>
       </c>
       <c r="C12" t="n">
-        <v>388080</v>
+        <v>296352</v>
       </c>
       <c r="D12" t="n">
-        <v>520764.05</v>
+        <v>986743.3</v>
       </c>
       <c r="E12" t="n">
-        <v>158520.1</v>
+        <v>296838</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>7215</v>
+        <v>21060</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19491,7 +20960,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6499.8</v>
+        <v>91800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,10 +20974,10 @@
         <v>429858</v>
       </c>
       <c r="C13" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D13" t="n">
-        <v>266701.98</v>
+        <v>505346.69</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -19514,7 +20986,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4995</v>
+        <v>14580</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19526,10 +20998,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>21334</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>2260.8</v>
+        <v>43200</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,10 +21015,10 @@
         <v>290070</v>
       </c>
       <c r="C14" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D14" t="n">
-        <v>78006.27</v>
+        <v>147806.21</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,10 +21056,10 @@
         <v>262944</v>
       </c>
       <c r="C15" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D15" t="n">
-        <v>39564.91</v>
+        <v>74967.55</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19590,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19605,7 +21083,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M15" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="16">
@@ -19628,7 +21109,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1110</v>
+        <v>3240</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -19643,7 +21124,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -19683,6 +21167,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19768,10 +21261,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D20" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -19795,6 +21288,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19835,6 +21331,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D24" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,7 +21621,7 @@
         <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>110400</v>
+        <v>110610</v>
       </c>
       <c r="H4" t="n">
         <v>28410</v>
@@ -20119,7 +21636,10 @@
         <v>216</v>
       </c>
       <c r="L4" t="n">
-        <v>310890</v>
+        <v>309930</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,10 +21662,10 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>54090</v>
+        <v>54210</v>
       </c>
       <c r="H5" t="n">
-        <v>18720</v>
+        <v>18750</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20157,7 +21677,10 @@
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>116730</v>
+        <v>117480</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>10920</v>
+        <v>11010</v>
       </c>
       <c r="H6" t="n">
-        <v>1170</v>
+        <v>1200</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>9</v>
       </c>
       <c r="L6" t="n">
-        <v>26160</v>
+        <v>25950</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20233,7 +21759,10 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>5160</v>
+        <v>5130</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -20256,7 +21785,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="H8" t="n">
         <v>60</v>
@@ -20272,6 +21801,9 @@
       </c>
       <c r="L8" t="n">
         <v>750</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20311,6 +21843,9 @@
       <c r="L9" t="n">
         <v>450</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>30</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21077,7 +22669,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6739.2</v>
+        <v>6750</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21086,10 +22678,13 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>33.1</v>
       </c>
       <c r="L5" t="n">
-        <v>24513.3</v>
+        <v>24670.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.4</v>
       </c>
       <c r="G6" t="n">
-        <v>546</v>
+        <v>550.5</v>
       </c>
       <c r="H6" t="n">
-        <v>666.9</v>
+        <v>684</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.85</v>
+        <v>4.56</v>
       </c>
       <c r="L6" t="n">
-        <v>9679.200000000001</v>
+        <v>9601.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>3096</v>
+        <v>3078</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21188,7 +22789,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>58.5</v>
+        <v>78</v>
       </c>
       <c r="H8" t="n">
         <v>51</v>
@@ -21204,6 +22805,9 @@
       </c>
       <c r="L8" t="n">
         <v>532.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21243,6 +22847,9 @@
       <c r="L9" t="n">
         <v>364.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>26.7</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>12396839.4</v>
       </c>
       <c r="C5" t="n">
-        <v>44625042</v>
+        <v>34077304.8</v>
       </c>
       <c r="D5" t="n">
-        <v>38876212.27</v>
+        <v>73662614.78</v>
       </c>
       <c r="E5" t="n">
-        <v>3438426.9</v>
+        <v>6438652.2</v>
       </c>
       <c r="F5" t="n">
         <v>4166.7</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1864399.68</v>
+        <v>38475000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>104999.4</v>
+        <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>896028</v>
+        <v>1607203.6</v>
       </c>
       <c r="L5" t="n">
-        <v>230915.29</v>
+        <v>4440744</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,22 +23699,22 @@
         <v>3647160</v>
       </c>
       <c r="C6" t="n">
-        <v>13147596</v>
+        <v>10039982.4</v>
       </c>
       <c r="D6" t="n">
-        <v>10721407.5</v>
+        <v>20314914.05</v>
       </c>
       <c r="E6" t="n">
-        <v>700572.6</v>
+        <v>1311862.5</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>10101</v>
+        <v>29727</v>
       </c>
       <c r="H6" t="n">
-        <v>184497.88</v>
+        <v>3898800</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22056,10 +23723,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>124803.9</v>
+        <v>221561.03</v>
       </c>
       <c r="L6" t="n">
-        <v>91178.06</v>
+        <v>1728270</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>401405.4</v>
       </c>
       <c r="C7" t="n">
-        <v>1857240</v>
+        <v>1418256</v>
       </c>
       <c r="D7" t="n">
-        <v>1715255.06</v>
+        <v>3250063.87</v>
       </c>
       <c r="E7" t="n">
-        <v>211614.38</v>
+        <v>396260.1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1748.25</v>
+        <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>84820.89</v>
+        <v>1747620</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>17493.88</v>
+        <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>29164.32</v>
+        <v>554040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>79200</v>
       </c>
       <c r="C8" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D8" t="n">
-        <v>236265.89</v>
+        <v>447676.42</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1082.25</v>
+        <v>4212</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5016.15</v>
+        <v>95850</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>33660</v>
       </c>
       <c r="C9" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D9" t="n">
-        <v>64443.45</v>
+        <v>122107.39</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22161,7 +23837,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3433.59</v>
+        <v>65610</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22199,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>251.51</v>
+        <v>4806</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22251,6 +23933,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>32</v>
       </c>
       <c r="K4" t="n">
-        <v>960</v>
+        <v>345</v>
       </c>
       <c r="L4" t="n">
         <v>1308150</v>
@@ -590,7 +590,7 @@
         <v>18</v>
       </c>
       <c r="K5" t="n">
-        <v>557</v>
+        <v>164</v>
       </c>
       <c r="L5" t="n">
         <v>725310</v>
@@ -631,7 +631,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>59</v>
       </c>
       <c r="L6" t="n">
         <v>331110</v>
@@ -672,7 +672,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="L7" t="n">
         <v>166920</v>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>71910</v>
@@ -754,7 +754,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>26910</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>9420</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>570</v>
@@ -1553,7 +1553,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>107160</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
         <v>91560</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>44400</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>19350</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>8190</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2040</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>16.88</v>
+        <v>3.97</v>
       </c>
       <c r="L5" t="n">
         <v>19227.6</v>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>15.21</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>16428</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>5.74</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>11610</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>5814.9</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>1652.4</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>819673.84</v>
+        <v>192864.43</v>
       </c>
       <c r="L5" t="n">
         <v>3460968</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>738536.76</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
         <v>2957040</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>278808.55</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2089800</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>142948.86</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1046682</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>116971.4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>297432</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="L4" t="n">
         <v>86520</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L5" t="n">
         <v>25260</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.97</v>
+        <v>1.99</v>
       </c>
       <c r="L5" t="n">
         <v>5304.6</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>192864.43</v>
+        <v>96432.22</v>
       </c>
       <c r="L5" t="n">
         <v>954828</v>
@@ -7577,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>27330</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>8190</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1380</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>30</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1719.9</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>510.6</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>18</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80360.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>309582</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>91908</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3240</v>
@@ -10589,7 +10589,7 @@
         <v>8</v>
       </c>
       <c r="K4" t="n">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="L4" t="n">
         <v>286830</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="L5" t="n">
         <v>180360</v>
@@ -10671,7 +10671,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
         <v>76800</v>
@@ -10712,7 +10712,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>36030</v>
@@ -10753,7 +10753,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>10440</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>3570</v>
@@ -11634,7 +11634,7 @@
         <v>5.4</v>
       </c>
       <c r="K5" t="n">
-        <v>184.37</v>
+        <v>54.28</v>
       </c>
       <c r="L5" t="n">
         <v>152315.1</v>
@@ -11675,7 +11675,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>123.71</v>
+        <v>29.91</v>
       </c>
       <c r="L6" t="n">
         <v>122510.7</v>
@@ -11716,7 +11716,7 @@
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>72.73</v>
+        <v>16.59</v>
       </c>
       <c r="L7" t="n">
         <v>100152</v>
@@ -11757,7 +11757,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>52.99</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
         <v>51056.1</v>
@@ -11798,7 +11798,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>20.88</v>
+        <v>2.41</v>
       </c>
       <c r="L9" t="n">
         <v>21797.1</v>
@@ -11839,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>8383.799999999999</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>570</v>
@@ -12638,7 +12638,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>57.59</v>
+        <v>18.54</v>
       </c>
       <c r="L5" t="n">
         <v>37875.6</v>
@@ -12679,7 +12679,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>38.53</v>
+        <v>11.15</v>
       </c>
       <c r="L6" t="n">
         <v>28416</v>
@@ -12720,7 +12720,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>13.4</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
         <v>21618</v>
@@ -12761,7 +12761,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>5.89</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>7412.4</v>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2891.7</v>
@@ -13642,7 +13642,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2796534.26</v>
+        <v>900034.02</v>
       </c>
       <c r="L5" t="n">
         <v>6817608</v>
@@ -13683,7 +13683,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1870959.79</v>
+        <v>541593.62</v>
       </c>
       <c r="L6" t="n">
         <v>5114880</v>
@@ -13724,7 +13724,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>650553.29</v>
+        <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
         <v>3891240</v>
@@ -13765,7 +13765,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>285897.73</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
         <v>1334232</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38990.47</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>520506</v>
@@ -14605,7 +14605,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
         <v>179490</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
         <v>46950</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.96</v>
+        <v>3.31</v>
       </c>
       <c r="L5" t="n">
         <v>9859.5</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241080.54</v>
+        <v>160720.36</v>
       </c>
       <c r="L5" t="n">
         <v>1774710</v>
@@ -17658,7 +17658,7 @@
         <v>131101.2</v>
       </c>
       <c r="K5" t="n">
-        <v>8952124.050000001</v>
+        <v>2635813.9</v>
       </c>
       <c r="L5" t="n">
         <v>27416718</v>
@@ -17699,7 +17699,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>6006765.65</v>
+        <v>1452455.63</v>
       </c>
       <c r="L6" t="n">
         <v>22051926</v>
@@ -17740,7 +17740,7 @@
         <v>84973</v>
       </c>
       <c r="K7" t="n">
-        <v>3531574.99</v>
+        <v>805446.9300000001</v>
       </c>
       <c r="L7" t="n">
         <v>18027360</v>
@@ -17781,7 +17781,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2573079.55</v>
+        <v>321634.94</v>
       </c>
       <c r="L8" t="n">
         <v>9190098</v>
@@ -17822,7 +17822,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>1013752.17</v>
+        <v>116971.4</v>
       </c>
       <c r="L9" t="n">
         <v>3923478</v>
@@ -17863,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>168974.88</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1509084</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>46103.92</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>102600</v>
@@ -18621,7 +18621,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>267</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>253590</v>
@@ -18662,7 +18662,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>197</v>
+        <v>62</v>
       </c>
       <c r="L5" t="n">
         <v>201210</v>
@@ -18703,7 +18703,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
         <v>131430</v>
@@ -18744,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
         <v>83400</v>
@@ -18785,7 +18785,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>43350</v>
@@ -18826,7 +18826,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>18210</v>
@@ -18867,7 +18867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>4080</v>
@@ -18990,7 +18990,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>240</v>
@@ -19666,7 +19666,7 @@
         <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>65.20999999999999</v>
+        <v>20.52</v>
       </c>
       <c r="L5" t="n">
         <v>42254.1</v>
@@ -19707,7 +19707,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>63.38</v>
+        <v>16.73</v>
       </c>
       <c r="L6" t="n">
         <v>48629.1</v>
@@ -19748,7 +19748,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>51.68</v>
+        <v>14.67</v>
       </c>
       <c r="L7" t="n">
         <v>50040</v>
@@ -19789,7 +19789,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>43.42</v>
+        <v>3.68</v>
       </c>
       <c r="L8" t="n">
         <v>30778.5</v>
@@ -19830,7 +19830,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>16.86</v>
+        <v>1.61</v>
       </c>
       <c r="L9" t="n">
         <v>14750.1</v>
@@ -19871,7 +19871,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>3631.2</v>
@@ -19994,7 +19994,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.95</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>240</v>
@@ -20670,7 +20670,7 @@
         <v>36417</v>
       </c>
       <c r="K5" t="n">
-        <v>3166191.09</v>
+        <v>996466.23</v>
       </c>
       <c r="L5" t="n">
         <v>7605738</v>
@@ -20711,7 +20711,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>3077236.5</v>
+        <v>812390.4399999999</v>
       </c>
       <c r="L6" t="n">
         <v>8753238</v>
@@ -20752,7 +20752,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2509276.97</v>
+        <v>712510.74</v>
       </c>
       <c r="L7" t="n">
         <v>9007200</v>
@@ -20793,7 +20793,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2108495.74</v>
+        <v>178686.08</v>
       </c>
       <c r="L8" t="n">
         <v>5540130</v>
@@ -20834,7 +20834,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>818799.83</v>
+        <v>77980.94</v>
       </c>
       <c r="L9" t="n">
         <v>2655018</v>
@@ -20875,7 +20875,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>168974.88</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>653616</v>
@@ -20998,7 +20998,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>46103.92</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>43200</v>
@@ -21633,7 +21633,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>216</v>
+        <v>66</v>
       </c>
       <c r="L4" t="n">
         <v>309930</v>
@@ -21674,7 +21674,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>117480</v>
@@ -21715,7 +21715,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>25950</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5130</v>
@@ -22678,7 +22678,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>33.1</v>
+        <v>5.96</v>
       </c>
       <c r="L5" t="n">
         <v>24670.8</v>
@@ -22719,7 +22719,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>4.56</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>9601.5</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>3078</v>
@@ -23682,7 +23682,7 @@
         <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1607203.6</v>
+        <v>289296.65</v>
       </c>
       <c r="L5" t="n">
         <v>4440744</v>
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>221561.03</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>1728270</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>30978.73</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>554040</v>

--- a/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_10yrs_Future_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>484140</v>
       </c>
       <c r="H4" t="n">
-        <v>63330</v>
+        <v>70830</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -572,22 +572,22 @@
         <v>345</v>
       </c>
       <c r="L4" t="n">
-        <v>1308150</v>
+        <v>1446150</v>
       </c>
       <c r="M4" t="n">
-        <v>62910</v>
+        <v>57180</v>
       </c>
       <c r="N4" t="n">
-        <v>48240</v>
+        <v>61980</v>
       </c>
       <c r="O4" t="n">
-        <v>247230</v>
+        <v>265560</v>
       </c>
       <c r="P4" t="n">
-        <v>69600</v>
+        <v>26970</v>
       </c>
       <c r="Q4" t="n">
-        <v>195114.86</v>
+        <v>2021956.37</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>303960</v>
       </c>
       <c r="H5" t="n">
-        <v>40590</v>
+        <v>46620</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -625,22 +625,22 @@
         <v>164</v>
       </c>
       <c r="L5" t="n">
-        <v>725310</v>
+        <v>819630</v>
       </c>
       <c r="M5" t="n">
-        <v>33750</v>
+        <v>50250</v>
       </c>
       <c r="N5" t="n">
-        <v>14370</v>
+        <v>18810</v>
       </c>
       <c r="O5" t="n">
-        <v>179520</v>
+        <v>208200</v>
       </c>
       <c r="P5" t="n">
-        <v>78030</v>
+        <v>59130</v>
       </c>
       <c r="Q5" t="n">
-        <v>136011.5</v>
+        <v>1409473.97</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>162450</v>
       </c>
       <c r="H6" t="n">
-        <v>6840</v>
+        <v>9060</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>59</v>
       </c>
       <c r="L6" t="n">
-        <v>331110</v>
+        <v>383700</v>
       </c>
       <c r="M6" t="n">
-        <v>14970</v>
+        <v>39210</v>
       </c>
       <c r="N6" t="n">
-        <v>3990</v>
+        <v>8370</v>
       </c>
       <c r="O6" t="n">
-        <v>79500</v>
+        <v>100440</v>
       </c>
       <c r="P6" t="n">
-        <v>81900</v>
+        <v>62160</v>
       </c>
       <c r="Q6" t="n">
-        <v>82881.75</v>
+        <v>858895.54</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>63480</v>
       </c>
       <c r="H7" t="n">
-        <v>1140</v>
+        <v>1680</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -731,22 +731,22 @@
         <v>26</v>
       </c>
       <c r="L7" t="n">
-        <v>166920</v>
+        <v>208350</v>
       </c>
       <c r="M7" t="n">
-        <v>8970</v>
+        <v>31350</v>
       </c>
       <c r="N7" t="n">
-        <v>270</v>
+        <v>1470</v>
       </c>
       <c r="O7" t="n">
-        <v>27540</v>
+        <v>50910</v>
       </c>
       <c r="P7" t="n">
-        <v>86910</v>
+        <v>85470</v>
       </c>
       <c r="Q7" t="n">
-        <v>42870.69</v>
+        <v>444264.85</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>27480</v>
       </c>
       <c r="H8" t="n">
-        <v>180</v>
+        <v>450</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -784,22 +784,22 @@
         <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>71910</v>
+        <v>112230</v>
       </c>
       <c r="M8" t="n">
-        <v>4440</v>
+        <v>28680</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>7080</v>
+        <v>19740</v>
       </c>
       <c r="P8" t="n">
-        <v>80940</v>
+        <v>88890</v>
       </c>
       <c r="Q8" t="n">
-        <v>23644.92</v>
+        <v>245029.97</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>18360</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>26910</v>
+        <v>62760</v>
       </c>
       <c r="M9" t="n">
-        <v>3150</v>
+        <v>24510</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>570</v>
+        <v>3930</v>
       </c>
       <c r="P9" t="n">
-        <v>81060</v>
+        <v>121620</v>
       </c>
       <c r="Q9" t="n">
-        <v>13338.1</v>
+        <v>138221.41</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>6090</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>9420</v>
+        <v>38940</v>
       </c>
       <c r="M10" t="n">
-        <v>1200</v>
+        <v>16620</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="P10" t="n">
-        <v>61980</v>
+        <v>106980</v>
       </c>
       <c r="Q10" t="n">
-        <v>6326.94</v>
+        <v>65565.45</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>1950</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -943,22 +943,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5190</v>
+        <v>32790</v>
       </c>
       <c r="M11" t="n">
-        <v>240</v>
+        <v>6240</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>36390</v>
+        <v>61380</v>
       </c>
       <c r="Q11" t="n">
-        <v>2580.53</v>
+        <v>26741.75</v>
       </c>
     </row>
     <row r="12">
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2130</v>
+        <v>14280</v>
       </c>
       <c r="M12" t="n">
-        <v>150</v>
+        <v>12420</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>36450</v>
+        <v>48420</v>
       </c>
       <c r="Q12" t="n">
-        <v>1497.67</v>
+        <v>15520.23</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>480</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>570</v>
+        <v>8430</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>2070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>33000</v>
+        <v>55290</v>
       </c>
       <c r="Q13" t="n">
-        <v>1286.52</v>
+        <v>13332.13</v>
       </c>
     </row>
     <row r="14">
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>870</v>
+        <v>5010</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>19740</v>
+        <v>29610</v>
       </c>
       <c r="Q14" t="n">
-        <v>1232.06</v>
+        <v>12767.76</v>
       </c>
     </row>
     <row r="15">
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>390</v>
+        <v>3660</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P15" t="n">
-        <v>21750</v>
+        <v>37650</v>
       </c>
       <c r="Q15" t="n">
-        <v>611.34</v>
+        <v>6335.31</v>
       </c>
     </row>
     <row r="16">
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>1770</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5040</v>
+        <v>9450</v>
       </c>
       <c r="Q16" t="n">
-        <v>208.69</v>
+        <v>2162.66</v>
       </c>
     </row>
     <row r="17">
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>630</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="n">
-        <v>43.75</v>
+        <v>453.35</v>
       </c>
     </row>
     <row r="18">
@@ -1314,7 +1314,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>570</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.79</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="19">
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -1852,7 +1852,7 @@
         <v>35670</v>
       </c>
       <c r="H4" t="n">
-        <v>4980</v>
+        <v>6570</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>107160</v>
+        <v>110160</v>
       </c>
       <c r="M4" t="n">
-        <v>11130</v>
+        <v>6660</v>
       </c>
       <c r="N4" t="n">
-        <v>720</v>
+        <v>1050</v>
       </c>
       <c r="O4" t="n">
-        <v>510</v>
+        <v>570</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1952.26</v>
+        <v>221256.36</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>35790</v>
       </c>
       <c r="H5" t="n">
-        <v>2820</v>
+        <v>2940</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>91560</v>
+        <v>103980</v>
       </c>
       <c r="M5" t="n">
-        <v>10470</v>
+        <v>14130</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O5" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2373.08</v>
+        <v>268949.52</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>21000</v>
       </c>
       <c r="H6" t="n">
-        <v>3570</v>
+        <v>4080</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1970,10 +1970,10 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>44400</v>
+        <v>56340</v>
       </c>
       <c r="M6" t="n">
-        <v>3210</v>
+        <v>10380</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1991.25</v>
+        <v>225675</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>7260</v>
       </c>
       <c r="H7" t="n">
-        <v>300</v>
+        <v>630</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>19350</v>
+        <v>27060</v>
       </c>
       <c r="M7" t="n">
-        <v>2100</v>
+        <v>5820</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1319.73</v>
+        <v>149569.74</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>7500</v>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8190</v>
+        <v>15510</v>
       </c>
       <c r="M8" t="n">
-        <v>660</v>
+        <v>3690</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>843.72</v>
+        <v>95621.94</v>
       </c>
     </row>
     <row r="9">
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2040</v>
+        <v>5070</v>
       </c>
       <c r="M9" t="n">
-        <v>60</v>
+        <v>1590</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>321.27</v>
+        <v>36410.94</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>300</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1170</v>
+        <v>2490</v>
       </c>
       <c r="M10" t="n">
-        <v>180</v>
+        <v>990</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>156.33</v>
+        <v>17717.4</v>
       </c>
     </row>
     <row r="11">
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>780</v>
+        <v>1560</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.15000000000001</v>
+        <v>10217.34</v>
       </c>
     </row>
     <row r="12">
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>810</v>
+        <v>1500</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.65000000000001</v>
+        <v>8913.780000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>120</v>
+        <v>1080</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>87.29000000000001</v>
+        <v>9892.98</v>
       </c>
     </row>
     <row r="14">
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>96.26000000000001</v>
+        <v>10908.9</v>
       </c>
     </row>
     <row r="15">
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.64</v>
+        <v>4265.64</v>
       </c>
     </row>
     <row r="16">
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.92</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="17">
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1015.2</v>
+        <v>1058.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>3.97</v>
       </c>
       <c r="L5" t="n">
-        <v>19227.6</v>
+        <v>21835.8</v>
       </c>
       <c r="M5" t="n">
-        <v>209.4</v>
+        <v>282.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>118.65</v>
+        <v>13447.48</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>1050</v>
       </c>
       <c r="H6" t="n">
-        <v>2034.9</v>
+        <v>2325.6</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -3262,10 +3262,10 @@
         <v>1.01</v>
       </c>
       <c r="L6" t="n">
-        <v>16428</v>
+        <v>20845.8</v>
       </c>
       <c r="M6" t="n">
-        <v>256.8</v>
+        <v>830.4</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1493.44</v>
+        <v>169256.25</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1089</v>
       </c>
       <c r="H7" t="n">
-        <v>219</v>
+        <v>459.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>11610</v>
+        <v>16236</v>
       </c>
       <c r="M7" t="n">
-        <v>735</v>
+        <v>2037</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1055.79</v>
+        <v>119655.79</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>4875</v>
       </c>
       <c r="H8" t="n">
-        <v>76.5</v>
+        <v>127.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5814.9</v>
+        <v>11012.1</v>
       </c>
       <c r="M8" t="n">
-        <v>363</v>
+        <v>2029.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>801.54</v>
+        <v>90840.84</v>
       </c>
     </row>
     <row r="9">
@@ -3421,10 +3421,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1652.4</v>
+        <v>4106.7</v>
       </c>
       <c r="M9" t="n">
-        <v>42</v>
+        <v>1113</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>311.63</v>
+        <v>35318.61</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>300</v>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1041.3</v>
+        <v>2216.1</v>
       </c>
       <c r="M10" t="n">
-        <v>153</v>
+        <v>841.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>156.33</v>
+        <v>17717.4</v>
       </c>
     </row>
     <row r="11">
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>780</v>
+        <v>1560</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>864</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>90.15000000000001</v>
+        <v>10217.34</v>
       </c>
     </row>
     <row r="12">
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>810</v>
+        <v>1500</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1083</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.65000000000001</v>
+        <v>8913.780000000001</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>120</v>
+        <v>1080</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>87.29000000000001</v>
+        <v>9892.98</v>
       </c>
     </row>
     <row r="14">
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>96.26000000000001</v>
+        <v>10908.9</v>
       </c>
     </row>
     <row r="15">
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37.64</v>
+        <v>4265.64</v>
       </c>
     </row>
     <row r="16">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.92</v>
+        <v>3277.26</v>
       </c>
     </row>
     <row r="17">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.43</v>
+        <v>48.96</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.51</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="19">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5786640</v>
+        <v>6032880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>192864.43</v>
       </c>
       <c r="L5" t="n">
-        <v>3460968</v>
+        <v>3930444</v>
       </c>
       <c r="M5" t="n">
-        <v>73290</v>
+        <v>98910</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="O5" t="n">
-        <v>2550</v>
+        <v>3315</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>71192.52</v>
+        <v>8068485.6</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>56700</v>
       </c>
       <c r="H6" t="n">
-        <v>11598930</v>
+        <v>13255920</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -4554,10 +4554,10 @@
         <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>2957040</v>
+        <v>3752244</v>
       </c>
       <c r="M6" t="n">
-        <v>89880</v>
+        <v>290640</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>896062.5</v>
+        <v>101553750</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>58806</v>
       </c>
       <c r="H7" t="n">
-        <v>1248300</v>
+        <v>2621430</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2089800</v>
+        <v>2922480</v>
       </c>
       <c r="M7" t="n">
-        <v>257250</v>
+        <v>712950</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5355</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>633471.84</v>
+        <v>71793475.2</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>263250</v>
       </c>
       <c r="H8" t="n">
-        <v>436050</v>
+        <v>726750</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,10 +4660,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1046682</v>
+        <v>1982178</v>
       </c>
       <c r="M8" t="n">
-        <v>127050</v>
+        <v>710325</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>480922.11</v>
+        <v>54504505.8</v>
       </c>
     </row>
     <row r="9">
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>297432</v>
+        <v>739206</v>
       </c>
       <c r="M9" t="n">
-        <v>14700</v>
+        <v>389550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>186980.89</v>
+        <v>21191167.08</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>16200</v>
       </c>
       <c r="H10" t="n">
-        <v>513000</v>
+        <v>1197000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>187434</v>
+        <v>398898</v>
       </c>
       <c r="M10" t="n">
-        <v>53550</v>
+        <v>294525</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>93798</v>
+        <v>10630440</v>
       </c>
     </row>
     <row r="11">
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>140400</v>
+        <v>280800</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>302400</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>54091.8</v>
+        <v>6130404</v>
       </c>
     </row>
     <row r="12">
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>145800</v>
+        <v>270000</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>379050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>47190.6</v>
+        <v>5348268</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>21600</v>
+        <v>194400</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>157500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>52374.6</v>
+        <v>5935788</v>
       </c>
     </row>
     <row r="14">
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>140400</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57753</v>
+        <v>6545340</v>
       </c>
     </row>
     <row r="15">
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>172800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22582.8</v>
+        <v>2559384</v>
       </c>
     </row>
     <row r="16">
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>64800</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17350.2</v>
+        <v>1966356</v>
       </c>
     </row>
     <row r="17">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>259.2</v>
+        <v>29376</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.8</v>
+        <v>34884</v>
       </c>
     </row>
     <row r="19">
@@ -5728,7 +5728,7 @@
         <v>26340</v>
       </c>
       <c r="H4" t="n">
-        <v>1560</v>
+        <v>2580</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>23</v>
       </c>
       <c r="L4" t="n">
-        <v>86520</v>
+        <v>104970</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2910</v>
+        <v>3810</v>
       </c>
       <c r="O4" t="n">
-        <v>17040</v>
+        <v>20130</v>
       </c>
       <c r="P4" t="n">
-        <v>9510</v>
+        <v>8190</v>
       </c>
       <c r="Q4" t="n">
-        <v>14780.15</v>
+        <v>77790.24000000001</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>5310</v>
       </c>
       <c r="H5" t="n">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>6</v>
       </c>
       <c r="L5" t="n">
-        <v>25260</v>
+        <v>36750</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1050</v>
+        <v>1440</v>
       </c>
       <c r="O5" t="n">
-        <v>2760</v>
+        <v>5670</v>
       </c>
       <c r="P5" t="n">
-        <v>7860</v>
+        <v>11430</v>
       </c>
       <c r="Q5" t="n">
-        <v>4171.51</v>
+        <v>21955.32</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1440</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>6360</v>
+        <v>10140</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5855,13 +5855,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>90</v>
+        <v>450</v>
       </c>
       <c r="P6" t="n">
-        <v>6030</v>
+        <v>8460</v>
       </c>
       <c r="Q6" t="n">
-        <v>238.24</v>
+        <v>1253.88</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>210</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1260</v>
+        <v>2700</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5760</v>
+        <v>9000</v>
       </c>
       <c r="Q7" t="n">
-        <v>64.64</v>
+        <v>340.2</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>210</v>
+        <v>1440</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4770</v>
+        <v>10530</v>
       </c>
       <c r="Q8" t="n">
-        <v>35.29</v>
+        <v>185.76</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3360</v>
+        <v>9570</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.7</v>
+        <v>103.68</v>
       </c>
     </row>
     <row r="10">
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>330</v>
+        <v>930</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.21</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>162</v>
+        <v>324</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>1.99</v>
       </c>
       <c r="L5" t="n">
-        <v>5304.6</v>
+        <v>7717.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.5</v>
+        <v>14.4</v>
       </c>
       <c r="O5" t="n">
-        <v>138</v>
+        <v>283.5</v>
       </c>
       <c r="P5" t="n">
-        <v>157.2</v>
+        <v>228.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>208.58</v>
+        <v>1097.77</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>72</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>2353.2</v>
+        <v>3751.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22.5</v>
+        <v>112.5</v>
       </c>
       <c r="P6" t="n">
-        <v>904.5</v>
+        <v>1269</v>
       </c>
       <c r="Q6" t="n">
-        <v>178.68</v>
+        <v>940.41</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>31.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>756</v>
+        <v>1620</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1440</v>
+        <v>2250</v>
       </c>
       <c r="Q7" t="n">
-        <v>51.71</v>
+        <v>272.16</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>149.1</v>
+        <v>1022.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1812.6</v>
+        <v>4001.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>33.53</v>
+        <v>176.47</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>486</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1680</v>
+        <v>4785</v>
       </c>
       <c r="Q9" t="n">
-        <v>19.11</v>
+        <v>100.57</v>
       </c>
     </row>
     <row r="10">
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>280.5</v>
+        <v>790.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.21</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>923400</v>
+        <v>1846800</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>96432.22</v>
       </c>
       <c r="L5" t="n">
-        <v>954828</v>
+        <v>1389150</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1785</v>
+        <v>2448</v>
       </c>
       <c r="O5" t="n">
-        <v>23460</v>
+        <v>48195</v>
       </c>
       <c r="P5" t="n">
-        <v>10218</v>
+        <v>14859</v>
       </c>
       <c r="Q5" t="n">
-        <v>125145.32</v>
+        <v>658659.6</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>3888</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>423576</v>
+        <v>675324</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3825</v>
+        <v>19125</v>
       </c>
       <c r="P6" t="n">
-        <v>58792.5</v>
+        <v>82485</v>
       </c>
       <c r="Q6" t="n">
-        <v>107206.74</v>
+        <v>564246</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>1701</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>136080</v>
+        <v>291600</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>93600</v>
+        <v>146250</v>
       </c>
       <c r="Q7" t="n">
-        <v>31026.24</v>
+        <v>163296</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>26838</v>
+        <v>184032</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>117819</v>
+        <v>260091</v>
       </c>
       <c r="Q8" t="n">
-        <v>20117.81</v>
+        <v>105883.2</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>87480</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>109200</v>
+        <v>311025</v>
       </c>
       <c r="Q9" t="n">
-        <v>11464.93</v>
+        <v>60341.76</v>
       </c>
     </row>
     <row r="10">
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>18232.5</v>
+        <v>51382.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>123.12</v>
+        <v>648</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>24120</v>
       </c>
       <c r="H4" t="n">
-        <v>3210</v>
+        <v>2700</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>27330</v>
+        <v>36300</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>13980</v>
+        <v>19020</v>
       </c>
       <c r="O4" t="n">
-        <v>28020</v>
+        <v>27480</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>11649.01</v>
+        <v>63211.68</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>6450</v>
       </c>
       <c r="H5" t="n">
-        <v>1920</v>
+        <v>2700</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8190</v>
+        <v>9810</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4590</v>
+        <v>3480</v>
       </c>
       <c r="O5" t="n">
-        <v>30660</v>
+        <v>29100</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1558.76</v>
+        <v>8458.379999999999</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>1770</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>540</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1380</v>
+        <v>4200</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1860</v>
+        <v>3690</v>
       </c>
       <c r="O6" t="n">
-        <v>15840</v>
+        <v>20520</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>295.47</v>
+        <v>1603.35</v>
       </c>
     </row>
     <row r="7">
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>120</v>
+        <v>1050</v>
       </c>
       <c r="O7" t="n">
-        <v>3300</v>
+        <v>6480</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>46.9</v>
+        <v>254.52</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>840</v>
+        <v>660</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.66</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.46</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>691.2</v>
+        <v>972</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1719.9</v>
+        <v>2060.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>45.9</v>
+        <v>34.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1533</v>
+        <v>1455</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>77.94</v>
+        <v>422.92</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>88.5</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>307.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>510.6</v>
+        <v>1554</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>93</v>
+        <v>184.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3960</v>
+        <v>5130</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>221.61</v>
+        <v>1202.51</v>
       </c>
     </row>
     <row r="7">
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8.4</v>
+        <v>73.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1155</v>
+        <v>2268</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>37.52</v>
+        <v>203.62</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>378</v>
+        <v>297</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.28</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>264</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.45</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3939840</v>
+        <v>5540400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>309582</v>
+        <v>370818</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7803</v>
+        <v>5916</v>
       </c>
       <c r="O5" t="n">
-        <v>260610</v>
+        <v>247350</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46762.76</v>
+        <v>253751.4</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>4779</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>1754460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>91908</v>
+        <v>279720</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>15810</v>
+        <v>31365</v>
       </c>
       <c r="O6" t="n">
-        <v>673200</v>
+        <v>872100</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>132963.53</v>
+        <v>721507.5</v>
       </c>
     </row>
     <row r="7">
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3240</v>
+        <v>16200</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1428</v>
+        <v>12495</v>
       </c>
       <c r="O7" t="n">
-        <v>196350</v>
+        <v>385560</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22514.11</v>
+        <v>122169.6</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>64260</v>
+        <v>50490</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4367.68</v>
+        <v>23700.6</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>44880</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>270.28</v>
+        <v>1466.64</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>111780</v>
       </c>
       <c r="H4" t="n">
-        <v>10770</v>
+        <v>12180</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -13492,19 +13492,19 @@
         <v>143</v>
       </c>
       <c r="L4" t="n">
-        <v>286830</v>
+        <v>277260</v>
       </c>
       <c r="M4" t="n">
-        <v>18420</v>
+        <v>3060</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>50520</v>
+        <v>49020</v>
       </c>
       <c r="P4" t="n">
-        <v>41520</v>
+        <v>11220</v>
       </c>
       <c r="Q4" t="n">
         <v>51127.31</v>
@@ -13533,7 +13533,7 @@
         <v>81000</v>
       </c>
       <c r="H5" t="n">
-        <v>11970</v>
+        <v>13020</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -13545,19 +13545,19 @@
         <v>56</v>
       </c>
       <c r="L5" t="n">
-        <v>180360</v>
+        <v>184680</v>
       </c>
       <c r="M5" t="n">
-        <v>11700</v>
+        <v>6690</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>52680</v>
+        <v>61590</v>
       </c>
       <c r="P5" t="n">
-        <v>40710</v>
+        <v>31350</v>
       </c>
       <c r="Q5" t="n">
         <v>46358.31</v>
@@ -13586,7 +13586,7 @@
         <v>42510</v>
       </c>
       <c r="H6" t="n">
-        <v>1380</v>
+        <v>1800</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -13598,19 +13598,19 @@
         <v>22</v>
       </c>
       <c r="L6" t="n">
-        <v>76800</v>
+        <v>75720</v>
       </c>
       <c r="M6" t="n">
-        <v>4590</v>
+        <v>8760</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>18480</v>
+        <v>22950</v>
       </c>
       <c r="P6" t="n">
-        <v>37560</v>
+        <v>34530</v>
       </c>
       <c r="Q6" t="n">
         <v>28592.59</v>
@@ -13639,7 +13639,7 @@
         <v>10410</v>
       </c>
       <c r="H7" t="n">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -13651,19 +13651,19 @@
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>36030</v>
+        <v>43380</v>
       </c>
       <c r="M7" t="n">
-        <v>2430</v>
+        <v>10680</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10080</v>
+        <v>12600</v>
       </c>
       <c r="P7" t="n">
-        <v>38670</v>
+        <v>41220</v>
       </c>
       <c r="Q7" t="n">
         <v>8062.1</v>
@@ -13692,7 +13692,7 @@
         <v>1560</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -13704,19 +13704,19 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>10440</v>
+        <v>22500</v>
       </c>
       <c r="M8" t="n">
-        <v>1170</v>
+        <v>12240</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2670</v>
+        <v>4560</v>
       </c>
       <c r="P8" t="n">
-        <v>38460</v>
+        <v>41550</v>
       </c>
       <c r="Q8" t="n">
         <v>1430.6</v>
@@ -13757,19 +13757,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>3570</v>
+        <v>23100</v>
       </c>
       <c r="M9" t="n">
-        <v>570</v>
+        <v>10680</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P9" t="n">
-        <v>38040</v>
+        <v>57720</v>
       </c>
       <c r="Q9" t="n">
         <v>286.81</v>
@@ -13810,19 +13810,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2970</v>
+        <v>21660</v>
       </c>
       <c r="M10" t="n">
-        <v>210</v>
+        <v>7680</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P10" t="n">
-        <v>28770</v>
+        <v>50790</v>
       </c>
       <c r="Q10" t="n">
         <v>225.1</v>
@@ -13851,7 +13851,7 @@
         <v>120</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13863,10 +13863,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2340</v>
+        <v>23370</v>
       </c>
       <c r="M11" t="n">
-        <v>120</v>
+        <v>3780</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>19410</v>
+        <v>37410</v>
       </c>
       <c r="Q11" t="n">
         <v>72.65000000000001</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>720</v>
+        <v>9240</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>8340</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12660</v>
+        <v>16800</v>
       </c>
       <c r="Q12" t="n">
         <v>30.13</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>4950</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14580</v>
+        <v>30120</v>
       </c>
       <c r="Q13" t="n">
         <v>17.63</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>240</v>
+        <v>2550</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6540</v>
+        <v>16740</v>
       </c>
       <c r="Q14" t="n">
         <v>8.48</v>
@@ -14075,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>1440</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>840</v>
+        <v>2340</v>
       </c>
       <c r="Q15" t="n">
         <v>4.58</v>
@@ -14128,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5600000000000001</v>
@@ -14181,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>14612.4</v>
+        <v>16783.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.32</v>
@@ -14837,22 +14837,22 @@
         <v>54.28</v>
       </c>
       <c r="L5" t="n">
-        <v>152315.1</v>
+        <v>172122.3</v>
       </c>
       <c r="M5" t="n">
-        <v>675</v>
+        <v>1005</v>
       </c>
       <c r="N5" t="n">
-        <v>143.7</v>
+        <v>188.1</v>
       </c>
       <c r="O5" t="n">
-        <v>8976</v>
+        <v>10410</v>
       </c>
       <c r="P5" t="n">
-        <v>1560.6</v>
+        <v>1182.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>6800.57</v>
+        <v>70473.7</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>8122.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3898.8</v>
+        <v>5164.2</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>29.91</v>
       </c>
       <c r="L6" t="n">
-        <v>122510.7</v>
+        <v>141969</v>
       </c>
       <c r="M6" t="n">
-        <v>1197.6</v>
+        <v>3136.8</v>
       </c>
       <c r="N6" t="n">
-        <v>199.5</v>
+        <v>418.5</v>
       </c>
       <c r="O6" t="n">
-        <v>19875</v>
+        <v>25110</v>
       </c>
       <c r="P6" t="n">
-        <v>12285</v>
+        <v>9324</v>
       </c>
       <c r="Q6" t="n">
-        <v>62161.31</v>
+        <v>644171.66</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>9522</v>
       </c>
       <c r="H7" t="n">
-        <v>832.2</v>
+        <v>1226.4</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -14943,22 +14943,22 @@
         <v>16.59</v>
       </c>
       <c r="L7" t="n">
-        <v>100152</v>
+        <v>125010</v>
       </c>
       <c r="M7" t="n">
-        <v>3139.5</v>
+        <v>10972.5</v>
       </c>
       <c r="N7" t="n">
-        <v>18.9</v>
+        <v>102.9</v>
       </c>
       <c r="O7" t="n">
-        <v>9639</v>
+        <v>17818.5</v>
       </c>
       <c r="P7" t="n">
-        <v>21727.5</v>
+        <v>21367.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>34296.55</v>
+        <v>355411.88</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>17862</v>
       </c>
       <c r="H8" t="n">
-        <v>153</v>
+        <v>382.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -14996,22 +14996,22 @@
         <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>51056.1</v>
+        <v>79683.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2442</v>
+        <v>15774</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>3186</v>
+        <v>8883</v>
       </c>
       <c r="P8" t="n">
-        <v>30757.2</v>
+        <v>33778.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>22462.67</v>
+        <v>232778.47</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>15606</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>330</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>2.41</v>
       </c>
       <c r="L9" t="n">
-        <v>21797.1</v>
+        <v>50835.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2205</v>
+        <v>17157</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>313.5</v>
+        <v>2161.5</v>
       </c>
       <c r="P9" t="n">
-        <v>40530</v>
+        <v>60810</v>
       </c>
       <c r="Q9" t="n">
-        <v>12937.95</v>
+        <v>134074.77</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>6090</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>420</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8383.799999999999</v>
+        <v>34656.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1020</v>
+        <v>14127</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="P10" t="n">
-        <v>52683</v>
+        <v>90933</v>
       </c>
       <c r="Q10" t="n">
-        <v>6326.94</v>
+        <v>65565.45</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>1950</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15155,22 +15155,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5190</v>
+        <v>32790</v>
       </c>
       <c r="M11" t="n">
-        <v>216</v>
+        <v>5616</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
-        <v>32751</v>
+        <v>55242</v>
       </c>
       <c r="Q11" t="n">
-        <v>2580.53</v>
+        <v>26741.75</v>
       </c>
     </row>
     <row r="12">
@@ -15208,10 +15208,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2130</v>
+        <v>14280</v>
       </c>
       <c r="M12" t="n">
-        <v>142.5</v>
+        <v>11799</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -15220,10 +15220,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>36450</v>
+        <v>48420</v>
       </c>
       <c r="Q12" t="n">
-        <v>1497.67</v>
+        <v>15520.23</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>480</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,10 +15261,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>570</v>
+        <v>8430</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>2070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -15273,10 +15273,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>33000</v>
+        <v>55290</v>
       </c>
       <c r="Q13" t="n">
-        <v>1286.52</v>
+        <v>13332.13</v>
       </c>
     </row>
     <row r="14">
@@ -15314,10 +15314,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>870</v>
+        <v>5010</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>19740</v>
+        <v>29610</v>
       </c>
       <c r="Q14" t="n">
-        <v>1232.06</v>
+        <v>12767.76</v>
       </c>
     </row>
     <row r="15">
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>390</v>
+        <v>3660</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>300</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P15" t="n">
-        <v>21750</v>
+        <v>37650</v>
       </c>
       <c r="Q15" t="n">
-        <v>611.34</v>
+        <v>6335.31</v>
       </c>
     </row>
     <row r="16">
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>1770</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>5040</v>
+        <v>9450</v>
       </c>
       <c r="Q16" t="n">
-        <v>208.69</v>
+        <v>2162.66</v>
       </c>
     </row>
     <row r="17">
@@ -15473,7 +15473,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>630</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="n">
-        <v>43.75</v>
+        <v>453.35</v>
       </c>
     </row>
     <row r="18">
@@ -15526,7 +15526,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>570</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.79</v>
+        <v>39.32</v>
       </c>
     </row>
     <row r="19">
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="20">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4309.2</v>
+        <v>4687.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.32</v>
@@ -16129,19 +16129,19 @@
         <v>18.54</v>
       </c>
       <c r="L5" t="n">
-        <v>37875.6</v>
+        <v>38782.8</v>
       </c>
       <c r="M5" t="n">
-        <v>234</v>
+        <v>133.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2634</v>
+        <v>3079.5</v>
       </c>
       <c r="P5" t="n">
-        <v>814.2</v>
+        <v>627</v>
       </c>
       <c r="Q5" t="n">
         <v>2317.92</v>
@@ -16170,7 +16170,7 @@
         <v>2125.5</v>
       </c>
       <c r="H6" t="n">
-        <v>786.6</v>
+        <v>1026</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -16182,19 +16182,19 @@
         <v>11.15</v>
       </c>
       <c r="L6" t="n">
-        <v>28416</v>
+        <v>28016.4</v>
       </c>
       <c r="M6" t="n">
-        <v>367.2</v>
+        <v>700.8</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4620</v>
+        <v>5737.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5634</v>
+        <v>5179.5</v>
       </c>
       <c r="Q6" t="n">
         <v>21444.44</v>
@@ -16223,7 +16223,7 @@
         <v>1561.5</v>
       </c>
       <c r="H7" t="n">
-        <v>306.6</v>
+        <v>372.3</v>
       </c>
       <c r="I7" t="n">
         <v>0.64</v>
@@ -16235,19 +16235,19 @@
         <v>1.91</v>
       </c>
       <c r="L7" t="n">
-        <v>21618</v>
+        <v>26028</v>
       </c>
       <c r="M7" t="n">
-        <v>850.5</v>
+        <v>3738</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3528</v>
+        <v>4410</v>
       </c>
       <c r="P7" t="n">
-        <v>9667.5</v>
+        <v>10305</v>
       </c>
       <c r="Q7" t="n">
         <v>6449.68</v>
@@ -16276,7 +16276,7 @@
         <v>1014</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -16288,19 +16288,19 @@
         <v>2.94</v>
       </c>
       <c r="L8" t="n">
-        <v>7412.4</v>
+        <v>15975</v>
       </c>
       <c r="M8" t="n">
-        <v>643.5</v>
+        <v>6732</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1201.5</v>
+        <v>2052</v>
       </c>
       <c r="P8" t="n">
-        <v>14614.8</v>
+        <v>15789</v>
       </c>
       <c r="Q8" t="n">
         <v>1359.07</v>
@@ -16341,19 +16341,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2891.7</v>
+        <v>18711</v>
       </c>
       <c r="M9" t="n">
-        <v>399</v>
+        <v>7476</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16.5</v>
+        <v>66</v>
       </c>
       <c r="P9" t="n">
-        <v>19020</v>
+        <v>28860</v>
       </c>
       <c r="Q9" t="n">
         <v>278.21</v>
@@ -16394,19 +16394,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2643.3</v>
+        <v>19277.4</v>
       </c>
       <c r="M10" t="n">
-        <v>178.5</v>
+        <v>6528</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="P10" t="n">
-        <v>24454.5</v>
+        <v>43171.5</v>
       </c>
       <c r="Q10" t="n">
         <v>225.1</v>
@@ -16435,7 +16435,7 @@
         <v>120</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -16447,10 +16447,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2340</v>
+        <v>23370</v>
       </c>
       <c r="M11" t="n">
-        <v>108</v>
+        <v>3402</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>17469</v>
+        <v>33669</v>
       </c>
       <c r="Q11" t="n">
         <v>72.65000000000001</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>720</v>
+        <v>9240</v>
       </c>
       <c r="M12" t="n">
-        <v>28.5</v>
+        <v>7923</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12660</v>
+        <v>16800</v>
       </c>
       <c r="Q12" t="n">
         <v>30.13</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>60</v>
+        <v>4950</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>14580</v>
+        <v>30120</v>
       </c>
       <c r="Q13" t="n">
         <v>17.63</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>240</v>
+        <v>2550</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>6540</v>
+        <v>16740</v>
       </c>
       <c r="Q14" t="n">
         <v>8.48</v>
@@ -16659,7 +16659,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>1440</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>840</v>
+        <v>2340</v>
       </c>
       <c r="Q15" t="n">
         <v>4.58</v>
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="Q16" t="n">
         <v>0.5600000000000001</v>
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>420</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>24562440</v>
+        <v>26717040</v>
       </c>
       <c r="I5" t="n">
         <v>257152.58</v>
@@ -17421,19 +17421,19 @@
         <v>900034.02</v>
       </c>
       <c r="L5" t="n">
-        <v>6817608</v>
+        <v>6980904</v>
       </c>
       <c r="M5" t="n">
-        <v>81900</v>
+        <v>46830</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>447780</v>
+        <v>523515</v>
       </c>
       <c r="P5" t="n">
-        <v>52923</v>
+        <v>40755</v>
       </c>
       <c r="Q5" t="n">
         <v>1390749.16</v>
@@ -17462,7 +17462,7 @@
         <v>114777</v>
       </c>
       <c r="H6" t="n">
-        <v>4483620</v>
+        <v>5848200</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -17474,19 +17474,19 @@
         <v>541593.62</v>
       </c>
       <c r="L6" t="n">
-        <v>5114880</v>
+        <v>5042952</v>
       </c>
       <c r="M6" t="n">
-        <v>128520</v>
+        <v>245280</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>785400</v>
+        <v>975375</v>
       </c>
       <c r="P6" t="n">
-        <v>366210</v>
+        <v>336667.5</v>
       </c>
       <c r="Q6" t="n">
         <v>12866665.32</v>
@@ -17515,7 +17515,7 @@
         <v>84321</v>
       </c>
       <c r="H7" t="n">
-        <v>1747620</v>
+        <v>2122110</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -17527,19 +17527,19 @@
         <v>92936.17999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3891240</v>
+        <v>4685040</v>
       </c>
       <c r="M7" t="n">
-        <v>297675</v>
+        <v>1308300</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>599760</v>
+        <v>749700</v>
       </c>
       <c r="P7" t="n">
-        <v>628387.5</v>
+        <v>669825</v>
       </c>
       <c r="Q7" t="n">
         <v>3869805.89</v>
@@ -17568,7 +17568,7 @@
         <v>54756</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>581400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -17580,19 +17580,19 @@
         <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>1334232</v>
+        <v>2875500</v>
       </c>
       <c r="M8" t="n">
-        <v>225225</v>
+        <v>2356200</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>204255</v>
+        <v>348840</v>
       </c>
       <c r="P8" t="n">
-        <v>949962</v>
+        <v>1026285</v>
       </c>
       <c r="Q8" t="n">
         <v>815442.23</v>
@@ -17633,19 +17633,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>520506</v>
+        <v>3367980</v>
       </c>
       <c r="M9" t="n">
-        <v>139650</v>
+        <v>2616600</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2805</v>
+        <v>11220</v>
       </c>
       <c r="P9" t="n">
-        <v>1236300</v>
+        <v>1875900</v>
       </c>
       <c r="Q9" t="n">
         <v>166924.58</v>
@@ -17686,19 +17686,19 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>475794</v>
+        <v>3469932</v>
       </c>
       <c r="M10" t="n">
-        <v>62475</v>
+        <v>2284800</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3570</v>
       </c>
       <c r="P10" t="n">
-        <v>1589542.5</v>
+        <v>2806147.5</v>
       </c>
       <c r="Q10" t="n">
         <v>135058.32</v>
@@ -17727,7 +17727,7 @@
         <v>6480</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -17739,10 +17739,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>421200</v>
+        <v>4206600</v>
       </c>
       <c r="M11" t="n">
-        <v>37800</v>
+        <v>1190700</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1135485</v>
+        <v>2188485</v>
       </c>
       <c r="Q11" t="n">
         <v>43590.96</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>129600</v>
+        <v>1663200</v>
       </c>
       <c r="M12" t="n">
-        <v>9975</v>
+        <v>2773050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>822900</v>
+        <v>1092000</v>
       </c>
       <c r="Q12" t="n">
         <v>18079.2</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10800</v>
+        <v>891000</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>63000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>947700</v>
+        <v>1957800</v>
       </c>
       <c r="Q13" t="n">
         <v>10579.68</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>43200</v>
+        <v>459000</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>425100</v>
+        <v>1088100</v>
       </c>
       <c r="Q14" t="n">
         <v>5088.96</v>
@@ -17951,7 +17951,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>54000</v>
+        <v>259200</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>54600</v>
+        <v>152100</v>
       </c>
       <c r="Q15" t="n">
         <v>2745.36</v>
@@ -18004,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>86400</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>19500</v>
+        <v>25350</v>
       </c>
       <c r="Q16" t="n">
         <v>334.8</v>
@@ -18057,7 +18057,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>102600</v>
+        <v>97200</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16200</v>
+        <v>75600</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>50220</v>
       </c>
       <c r="H4" t="n">
-        <v>3990</v>
+        <v>4710</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>179490</v>
+        <v>217410</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2850</v>
+        <v>3060</v>
       </c>
       <c r="O4" t="n">
-        <v>43800</v>
+        <v>52320</v>
       </c>
       <c r="P4" t="n">
-        <v>5280</v>
+        <v>3180</v>
       </c>
       <c r="Q4" t="n">
-        <v>16206.83</v>
+        <v>185703.21</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>10080</v>
       </c>
       <c r="H5" t="n">
-        <v>1050</v>
+        <v>1440</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>46950</v>
+        <v>64320</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>600</v>
+        <v>1470</v>
       </c>
       <c r="O5" t="n">
-        <v>17910</v>
+        <v>25590</v>
       </c>
       <c r="P5" t="n">
-        <v>3810</v>
+        <v>6390</v>
       </c>
       <c r="Q5" t="n">
-        <v>3461.44</v>
+        <v>39662.37</v>
       </c>
     </row>
     <row r="6">
@@ -18754,34 +18754,34 @@
         <v>840</v>
       </c>
       <c r="H6" t="n">
+        <v>270</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14910</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>210</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8760</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
-        <v>2820</v>
+        <v>4380</v>
       </c>
       <c r="P6" t="n">
-        <v>2640</v>
+        <v>5820</v>
       </c>
       <c r="Q6" t="n">
-        <v>292.64</v>
+        <v>3353.13</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>570</v>
+        <v>2100</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18828,13 +18828,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P7" t="n">
-        <v>3030</v>
+        <v>7980</v>
       </c>
       <c r="Q7" t="n">
-        <v>76.64</v>
+        <v>878.13</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>540</v>
+        <v>2070</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.59</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="9">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>378</v>
+        <v>518.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.31</v>
       </c>
       <c r="L5" t="n">
-        <v>9859.5</v>
+        <v>13507.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>14.7</v>
       </c>
       <c r="O5" t="n">
-        <v>895.5</v>
+        <v>1279.5</v>
       </c>
       <c r="P5" t="n">
-        <v>76.2</v>
+        <v>127.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>173.07</v>
+        <v>1983.12</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3241.2</v>
+        <v>5516.7</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="O6" t="n">
-        <v>705</v>
+        <v>1095</v>
       </c>
       <c r="P6" t="n">
-        <v>396</v>
+        <v>873</v>
       </c>
       <c r="Q6" t="n">
-        <v>219.48</v>
+        <v>2514.85</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>342</v>
+        <v>1260</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20120,13 +20120,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="P7" t="n">
-        <v>757.5</v>
+        <v>1995</v>
       </c>
       <c r="Q7" t="n">
-        <v>61.31</v>
+        <v>702.5</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>63.9</v>
+        <v>170.4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>205.2</v>
+        <v>786.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="9">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2154600</v>
+        <v>2954880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>160720.36</v>
       </c>
       <c r="L5" t="n">
-        <v>1774710</v>
+        <v>2431296</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1020</v>
+        <v>2499</v>
       </c>
       <c r="O5" t="n">
-        <v>152235</v>
+        <v>217515</v>
       </c>
       <c r="P5" t="n">
-        <v>4953</v>
+        <v>8307</v>
       </c>
       <c r="Q5" t="n">
-        <v>103843.3</v>
+        <v>1189871.1</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>2268</v>
       </c>
       <c r="H6" t="n">
-        <v>682290</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>583416</v>
+        <v>993006</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1785</v>
       </c>
       <c r="O6" t="n">
-        <v>119850</v>
+        <v>186150</v>
       </c>
       <c r="P6" t="n">
-        <v>25740</v>
+        <v>56745</v>
       </c>
       <c r="Q6" t="n">
-        <v>131686.56</v>
+        <v>1508908.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>61560</v>
+        <v>226800</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21412,13 +21412,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1785</v>
+        <v>7140</v>
       </c>
       <c r="P7" t="n">
-        <v>49237.5</v>
+        <v>129675</v>
       </c>
       <c r="Q7" t="n">
-        <v>36785.66</v>
+        <v>421502.4</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>11502</v>
+        <v>30672</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>13338</v>
+        <v>51129</v>
       </c>
       <c r="Q8" t="n">
-        <v>1477.44</v>
+        <v>16929</v>
       </c>
     </row>
     <row r="9">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>16200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>83290680</v>
+        <v>95664240</v>
       </c>
       <c r="I5" t="n">
         <v>257152.58</v>
@@ -22589,22 +22589,22 @@
         <v>2635813.9</v>
       </c>
       <c r="L5" t="n">
-        <v>27416718</v>
+        <v>30982014</v>
       </c>
       <c r="M5" t="n">
-        <v>236250</v>
+        <v>351750</v>
       </c>
       <c r="N5" t="n">
-        <v>24429</v>
+        <v>31977</v>
       </c>
       <c r="O5" t="n">
-        <v>1525920</v>
+        <v>1769700</v>
       </c>
       <c r="P5" t="n">
-        <v>101439</v>
+        <v>76869</v>
       </c>
       <c r="Q5" t="n">
-        <v>4080344.87</v>
+        <v>42284219</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>438615</v>
       </c>
       <c r="H6" t="n">
-        <v>22223160</v>
+        <v>29435940</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>1452455.63</v>
       </c>
       <c r="L6" t="n">
-        <v>22051926</v>
+        <v>25554420</v>
       </c>
       <c r="M6" t="n">
-        <v>419160</v>
+        <v>1097880</v>
       </c>
       <c r="N6" t="n">
-        <v>33915</v>
+        <v>71145</v>
       </c>
       <c r="O6" t="n">
-        <v>3378750</v>
+        <v>4268700</v>
       </c>
       <c r="P6" t="n">
-        <v>798525</v>
+        <v>606060</v>
       </c>
       <c r="Q6" t="n">
-        <v>37296786.96</v>
+        <v>386502993.9</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>514188</v>
       </c>
       <c r="H7" t="n">
-        <v>4743540</v>
+        <v>6990480</v>
       </c>
       <c r="I7" t="n">
         <v>123914.91</v>
@@ -22695,22 +22695,22 @@
         <v>805446.9300000001</v>
       </c>
       <c r="L7" t="n">
-        <v>18027360</v>
+        <v>22501800</v>
       </c>
       <c r="M7" t="n">
-        <v>1098825</v>
+        <v>3840375</v>
       </c>
       <c r="N7" t="n">
-        <v>3213</v>
+        <v>17493</v>
       </c>
       <c r="O7" t="n">
-        <v>1638630</v>
+        <v>3029145</v>
       </c>
       <c r="P7" t="n">
-        <v>1412287.5</v>
+        <v>1388887.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>20577932.93</v>
+        <v>213247127.52</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>964548</v>
       </c>
       <c r="H8" t="n">
-        <v>872100</v>
+        <v>2180250</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22748,22 +22748,22 @@
         <v>321634.94</v>
       </c>
       <c r="L8" t="n">
-        <v>9190098</v>
+        <v>14342994</v>
       </c>
       <c r="M8" t="n">
-        <v>854700</v>
+        <v>5520900</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>541620</v>
+        <v>1510110</v>
       </c>
       <c r="P8" t="n">
-        <v>1999218</v>
+        <v>2195583</v>
       </c>
       <c r="Q8" t="n">
-        <v>13477601.66</v>
+        <v>139667081.76</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>842724</v>
       </c>
       <c r="H9" t="n">
-        <v>513000</v>
+        <v>1881000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>116971.4</v>
       </c>
       <c r="L9" t="n">
-        <v>3923478</v>
+        <v>9150408</v>
       </c>
       <c r="M9" t="n">
-        <v>771750</v>
+        <v>6004950</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>53295</v>
+        <v>367455</v>
       </c>
       <c r="P9" t="n">
-        <v>2634450</v>
+        <v>3952650</v>
       </c>
       <c r="Q9" t="n">
-        <v>7762772.57</v>
+        <v>80444860.91</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>328860</v>
       </c>
       <c r="H10" t="n">
-        <v>855000</v>
+        <v>2394000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509084</v>
+        <v>6238188</v>
       </c>
       <c r="M10" t="n">
-        <v>357000</v>
+        <v>4944450</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>42840</v>
       </c>
       <c r="P10" t="n">
-        <v>3424395</v>
+        <v>5910645</v>
       </c>
       <c r="Q10" t="n">
-        <v>3796163.28</v>
+        <v>39339272.7</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>105300</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22907,22 +22907,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>934200</v>
+        <v>5902200</v>
       </c>
       <c r="M11" t="n">
-        <v>75600</v>
+        <v>1965600</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
-        <v>2128815</v>
+        <v>3590730</v>
       </c>
       <c r="Q11" t="n">
-        <v>1548316.08</v>
+        <v>16045049.7</v>
       </c>
     </row>
     <row r="12">
@@ -22960,10 +22960,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>383400</v>
+        <v>2570400</v>
       </c>
       <c r="M12" t="n">
-        <v>49875</v>
+        <v>4129650</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -22972,10 +22972,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2369250</v>
+        <v>3147300</v>
       </c>
       <c r="Q12" t="n">
-        <v>898603.2</v>
+        <v>9312138</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>25920</v>
       </c>
       <c r="H13" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,10 +23013,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>102600</v>
+        <v>1517400</v>
       </c>
       <c r="M13" t="n">
-        <v>10500</v>
+        <v>724500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2145000</v>
+        <v>3593850</v>
       </c>
       <c r="Q13" t="n">
-        <v>771914.88</v>
+        <v>7999279.2</v>
       </c>
     </row>
     <row r="14">
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>156600</v>
+        <v>901800</v>
       </c>
       <c r="M14" t="n">
-        <v>21000</v>
+        <v>115500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23078,10 +23078,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1283100</v>
+        <v>1924650</v>
       </c>
       <c r="Q14" t="n">
-        <v>739238.4</v>
+        <v>7660656</v>
       </c>
     </row>
     <row r="15">
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>70200</v>
+        <v>658800</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>105000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P15" t="n">
-        <v>1413750</v>
+        <v>2447250</v>
       </c>
       <c r="Q15" t="n">
-        <v>366806.88</v>
+        <v>3801184.2</v>
       </c>
     </row>
     <row r="16">
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>59400</v>
+        <v>318600</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>327600</v>
+        <v>614250</v>
       </c>
       <c r="Q16" t="n">
-        <v>125215.2</v>
+        <v>1297593</v>
       </c>
     </row>
     <row r="17">
@@ -23225,7 +23225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>102600</v>
+        <v>113400</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5850</v>
       </c>
       <c r="Q17" t="n">
-        <v>26248.32</v>
+        <v>272008.8</v>
       </c>
     </row>
     <row r="18">
@@ -23278,7 +23278,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16200</v>
+        <v>102600</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -23293,7 +23293,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2276.64</v>
+        <v>23592.6</v>
       </c>
     </row>
     <row r="19">
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>133.92</v>
+        <v>1387.8</v>
       </c>
     </row>
     <row r="20">
@@ -23816,7 +23816,7 @@
         <v>98430</v>
       </c>
       <c r="H4" t="n">
-        <v>6030</v>
+        <v>7650</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -23828,22 +23828,22 @@
         <v>76</v>
       </c>
       <c r="L4" t="n">
-        <v>253590</v>
+        <v>280200</v>
       </c>
       <c r="M4" t="n">
-        <v>26190</v>
+        <v>43830</v>
       </c>
       <c r="N4" t="n">
-        <v>14430</v>
+        <v>19620</v>
       </c>
       <c r="O4" t="n">
-        <v>24540</v>
+        <v>29070</v>
       </c>
       <c r="P4" t="n">
-        <v>6330</v>
+        <v>3660</v>
       </c>
       <c r="Q4" t="n">
-        <v>32500.14</v>
+        <v>318628.8</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>86820</v>
       </c>
       <c r="H5" t="n">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -23881,22 +23881,22 @@
         <v>62</v>
       </c>
       <c r="L5" t="n">
-        <v>201210</v>
+        <v>231030</v>
       </c>
       <c r="M5" t="n">
-        <v>7470</v>
+        <v>25800</v>
       </c>
       <c r="N5" t="n">
-        <v>3300</v>
+        <v>4590</v>
       </c>
       <c r="O5" t="n">
-        <v>25350</v>
+        <v>28920</v>
       </c>
       <c r="P5" t="n">
-        <v>10860</v>
+        <v>7230</v>
       </c>
       <c r="Q5" t="n">
-        <v>36279.73</v>
+        <v>355683.6</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>70290</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>131430</v>
+        <v>150960</v>
       </c>
       <c r="M6" t="n">
-        <v>4770</v>
+        <v>15990</v>
       </c>
       <c r="N6" t="n">
-        <v>870</v>
+        <v>1770</v>
       </c>
       <c r="O6" t="n">
-        <v>19440</v>
+        <v>25920</v>
       </c>
       <c r="P6" t="n">
-        <v>14730</v>
+        <v>8820</v>
       </c>
       <c r="Q6" t="n">
-        <v>26081.11</v>
+        <v>255697.2</v>
       </c>
     </row>
     <row r="7">
@@ -23987,22 +23987,22 @@
         <v>23</v>
       </c>
       <c r="L7" t="n">
-        <v>83400</v>
+        <v>100320</v>
       </c>
       <c r="M7" t="n">
-        <v>2850</v>
+        <v>7830</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>6630</v>
+        <v>15090</v>
       </c>
       <c r="P7" t="n">
-        <v>16170</v>
+        <v>13380</v>
       </c>
       <c r="Q7" t="n">
-        <v>17551.43</v>
+        <v>172072.8</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>14130</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>43350</v>
+        <v>58530</v>
       </c>
       <c r="M8" t="n">
-        <v>1890</v>
+        <v>7050</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1890</v>
+        <v>9030</v>
       </c>
       <c r="P8" t="n">
-        <v>14100</v>
+        <v>13620</v>
       </c>
       <c r="Q8" t="n">
-        <v>11428.73</v>
+        <v>112046.4</v>
       </c>
     </row>
     <row r="9">
@@ -24093,22 +24093,22 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>18210</v>
+        <v>27300</v>
       </c>
       <c r="M9" t="n">
-        <v>2370</v>
+        <v>6270</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>300</v>
+        <v>1740</v>
       </c>
       <c r="P9" t="n">
-        <v>15240</v>
+        <v>13710</v>
       </c>
       <c r="Q9" t="n">
-        <v>7244.76</v>
+        <v>71027.10000000001</v>
       </c>
     </row>
     <row r="10">
@@ -24146,22 +24146,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4080</v>
+        <v>9360</v>
       </c>
       <c r="M10" t="n">
-        <v>510</v>
+        <v>4470</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="P10" t="n">
-        <v>18210</v>
+        <v>24540</v>
       </c>
       <c r="Q10" t="n">
-        <v>3189.77</v>
+        <v>31272.3</v>
       </c>
     </row>
     <row r="11">
@@ -24199,22 +24199,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1620</v>
+        <v>5370</v>
       </c>
       <c r="M11" t="n">
-        <v>90</v>
+        <v>570</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>10710</v>
+        <v>11640</v>
       </c>
       <c r="Q11" t="n">
-        <v>997.77</v>
+        <v>9782.1</v>
       </c>
     </row>
     <row r="12">
@@ -24252,10 +24252,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>510</v>
+        <v>3060</v>
       </c>
       <c r="M12" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -24264,10 +24264,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>16650</v>
+        <v>16920</v>
       </c>
       <c r="Q12" t="n">
-        <v>373.9</v>
+        <v>3665.7</v>
       </c>
     </row>
     <row r="13">
@@ -24305,7 +24305,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>240</v>
+        <v>2280</v>
       </c>
       <c r="M13" t="n">
         <v>30</v>
@@ -24317,10 +24317,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15720</v>
+        <v>19800</v>
       </c>
       <c r="Q13" t="n">
-        <v>199.3</v>
+        <v>1953.9</v>
       </c>
     </row>
     <row r="14">
@@ -24358,10 +24358,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>90</v>
+        <v>1050</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -24370,10 +24370,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>12600</v>
+        <v>11730</v>
       </c>
       <c r="Q14" t="n">
-        <v>134.49</v>
+        <v>1318.5</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>90</v>
+        <v>1260</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P15" t="n">
-        <v>20910</v>
+        <v>35310</v>
       </c>
       <c r="Q15" t="n">
-        <v>121.91</v>
+        <v>1195.2</v>
       </c>
     </row>
     <row r="16">
@@ -24464,10 +24464,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>930</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4740</v>
+        <v>9060</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.09</v>
+        <v>275.4</v>
       </c>
     </row>
     <row r="17">
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.06</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="18">
@@ -24585,7 +24585,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>518.4</v>
+        <v>691.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -25173,22 +25173,22 @@
         <v>20.52</v>
       </c>
       <c r="L5" t="n">
-        <v>42254.1</v>
+        <v>48516.3</v>
       </c>
       <c r="M5" t="n">
-        <v>149.4</v>
+        <v>516</v>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>45.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1267.5</v>
+        <v>1446</v>
       </c>
       <c r="P5" t="n">
-        <v>217.2</v>
+        <v>144.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1813.99</v>
+        <v>17784.18</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3514.5</v>
       </c>
       <c r="H6" t="n">
-        <v>34.2</v>
+        <v>205.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>16.73</v>
       </c>
       <c r="L6" t="n">
-        <v>48629.1</v>
+        <v>55855.2</v>
       </c>
       <c r="M6" t="n">
-        <v>381.6</v>
+        <v>1279.2</v>
       </c>
       <c r="N6" t="n">
-        <v>43.5</v>
+        <v>88.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4860</v>
+        <v>6480</v>
       </c>
       <c r="P6" t="n">
-        <v>2209.5</v>
+        <v>1323</v>
       </c>
       <c r="Q6" t="n">
-        <v>19560.84</v>
+        <v>191772.9</v>
       </c>
     </row>
     <row r="7">
@@ -25279,22 +25279,22 @@
         <v>14.67</v>
       </c>
       <c r="L7" t="n">
-        <v>50040</v>
+        <v>60192</v>
       </c>
       <c r="M7" t="n">
-        <v>997.5</v>
+        <v>2740.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>2320.5</v>
+        <v>5281.5</v>
       </c>
       <c r="P7" t="n">
-        <v>4042.5</v>
+        <v>3345</v>
       </c>
       <c r="Q7" t="n">
-        <v>14041.14</v>
+        <v>137658.24</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>9184.5</v>
       </c>
       <c r="H8" t="n">
-        <v>25.5</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>3.68</v>
       </c>
       <c r="L8" t="n">
-        <v>30778.5</v>
+        <v>41556.3</v>
       </c>
       <c r="M8" t="n">
-        <v>1039.5</v>
+        <v>3877.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>850.5</v>
+        <v>4063.5</v>
       </c>
       <c r="P8" t="n">
-        <v>5358</v>
+        <v>5175.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>10857.3</v>
+        <v>106444.08</v>
       </c>
     </row>
     <row r="9">
@@ -25385,22 +25385,22 @@
         <v>1.61</v>
       </c>
       <c r="L9" t="n">
-        <v>14750.1</v>
+        <v>22113</v>
       </c>
       <c r="M9" t="n">
-        <v>1659</v>
+        <v>4389</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>957</v>
       </c>
       <c r="P9" t="n">
-        <v>7620</v>
+        <v>6855</v>
       </c>
       <c r="Q9" t="n">
-        <v>7027.42</v>
+        <v>68896.28999999999</v>
       </c>
     </row>
     <row r="10">
@@ -25438,22 +25438,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3631.2</v>
+        <v>8330.4</v>
       </c>
       <c r="M10" t="n">
-        <v>433.5</v>
+        <v>3799.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="P10" t="n">
-        <v>15478.5</v>
+        <v>20859</v>
       </c>
       <c r="Q10" t="n">
-        <v>3189.77</v>
+        <v>31272.3</v>
       </c>
     </row>
     <row r="11">
@@ -25491,22 +25491,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1620</v>
+        <v>5370</v>
       </c>
       <c r="M11" t="n">
-        <v>81</v>
+        <v>513</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
-        <v>9639</v>
+        <v>10476</v>
       </c>
       <c r="Q11" t="n">
-        <v>997.77</v>
+        <v>9782.1</v>
       </c>
     </row>
     <row r="12">
@@ -25544,10 +25544,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>510</v>
+        <v>3060</v>
       </c>
       <c r="M12" t="n">
-        <v>114</v>
+        <v>85.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -25556,10 +25556,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>16650</v>
+        <v>16920</v>
       </c>
       <c r="Q12" t="n">
-        <v>373.9</v>
+        <v>3665.7</v>
       </c>
     </row>
     <row r="13">
@@ -25597,7 +25597,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>240</v>
+        <v>2280</v>
       </c>
       <c r="M13" t="n">
         <v>30</v>
@@ -25609,10 +25609,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15720</v>
+        <v>19800</v>
       </c>
       <c r="Q13" t="n">
-        <v>199.3</v>
+        <v>1953.9</v>
       </c>
     </row>
     <row r="14">
@@ -25650,10 +25650,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>90</v>
+        <v>1050</v>
       </c>
       <c r="M14" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>12600</v>
+        <v>11730</v>
       </c>
       <c r="Q14" t="n">
-        <v>134.49</v>
+        <v>1318.5</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>90</v>
+        <v>1260</v>
       </c>
       <c r="M15" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P15" t="n">
-        <v>20910</v>
+        <v>35310</v>
       </c>
       <c r="Q15" t="n">
-        <v>121.91</v>
+        <v>1195.2</v>
       </c>
     </row>
     <row r="16">
@@ -25756,10 +25756,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>30</v>
+        <v>930</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25768,10 +25768,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4740</v>
+        <v>9060</v>
       </c>
       <c r="Q16" t="n">
-        <v>28.09</v>
+        <v>275.4</v>
       </c>
     </row>
     <row r="17">
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.06</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="18">
@@ -25877,7 +25877,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="19">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2954880</v>
+        <v>3939840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -26465,22 +26465,22 @@
         <v>996466.23</v>
       </c>
       <c r="L5" t="n">
-        <v>7605738</v>
+        <v>8732934</v>
       </c>
       <c r="M5" t="n">
-        <v>52290</v>
+        <v>180600</v>
       </c>
       <c r="N5" t="n">
-        <v>5610</v>
+        <v>7803</v>
       </c>
       <c r="O5" t="n">
-        <v>215475</v>
+        <v>245820</v>
       </c>
       <c r="P5" t="n">
-        <v>14118</v>
+        <v>9399</v>
       </c>
       <c r="Q5" t="n">
-        <v>1088391.82</v>
+        <v>10670508</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>189783</v>
       </c>
       <c r="H6" t="n">
-        <v>194940</v>
+        <v>1169640</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>812390.4399999999</v>
       </c>
       <c r="L6" t="n">
-        <v>8753238</v>
+        <v>10053936</v>
       </c>
       <c r="M6" t="n">
-        <v>133560</v>
+        <v>447720</v>
       </c>
       <c r="N6" t="n">
-        <v>7395</v>
+        <v>15045</v>
       </c>
       <c r="O6" t="n">
-        <v>826200</v>
+        <v>1101600</v>
       </c>
       <c r="P6" t="n">
-        <v>143617.5</v>
+        <v>85995</v>
       </c>
       <c r="Q6" t="n">
-        <v>11736501.48</v>
+        <v>115063740</v>
       </c>
     </row>
     <row r="7">
@@ -26571,22 +26571,22 @@
         <v>712510.74</v>
       </c>
       <c r="L7" t="n">
-        <v>9007200</v>
+        <v>10834560</v>
       </c>
       <c r="M7" t="n">
-        <v>349125</v>
+        <v>959175</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="O7" t="n">
-        <v>394485</v>
+        <v>897855</v>
       </c>
       <c r="P7" t="n">
-        <v>262762.5</v>
+        <v>217425</v>
       </c>
       <c r="Q7" t="n">
-        <v>8424684.289999999</v>
+        <v>82594944</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>495963</v>
       </c>
       <c r="H8" t="n">
-        <v>145350</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>178686.08</v>
       </c>
       <c r="L8" t="n">
-        <v>5540130</v>
+        <v>7480134</v>
       </c>
       <c r="M8" t="n">
-        <v>363825</v>
+        <v>1357125</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>144585</v>
+        <v>690795</v>
       </c>
       <c r="P8" t="n">
-        <v>348270</v>
+        <v>336414</v>
       </c>
       <c r="Q8" t="n">
-        <v>6514377.7</v>
+        <v>63866448</v>
       </c>
     </row>
     <row r="9">
@@ -26677,22 +26677,22 @@
         <v>77980.94</v>
       </c>
       <c r="L9" t="n">
-        <v>2655018</v>
+        <v>3980340</v>
       </c>
       <c r="M9" t="n">
-        <v>580650</v>
+        <v>1536150</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>28050</v>
+        <v>162690</v>
       </c>
       <c r="P9" t="n">
-        <v>495300</v>
+        <v>445575</v>
       </c>
       <c r="Q9" t="n">
-        <v>4216452.76</v>
+        <v>41337772.2</v>
       </c>
     </row>
     <row r="10">
@@ -26730,22 +26730,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>653616</v>
+        <v>1499472</v>
       </c>
       <c r="M10" t="n">
-        <v>151725</v>
+        <v>1329825</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>39270</v>
       </c>
       <c r="P10" t="n">
-        <v>1006102.5</v>
+        <v>1355835</v>
       </c>
       <c r="Q10" t="n">
-        <v>1913864.76</v>
+        <v>18763380</v>
       </c>
     </row>
     <row r="11">
@@ -26783,22 +26783,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>291600</v>
+        <v>966600</v>
       </c>
       <c r="M11" t="n">
-        <v>28350</v>
+        <v>179550</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
-        <v>626535</v>
+        <v>680940</v>
       </c>
       <c r="Q11" t="n">
-        <v>598664.52</v>
+        <v>5869260</v>
       </c>
     </row>
     <row r="12">
@@ -26836,10 +26836,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>91800</v>
+        <v>550800</v>
       </c>
       <c r="M12" t="n">
-        <v>39900</v>
+        <v>29925</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -26848,10 +26848,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1082250</v>
+        <v>1099800</v>
       </c>
       <c r="Q12" t="n">
-        <v>224340.84</v>
+        <v>2199420</v>
       </c>
     </row>
     <row r="13">
@@ -26889,7 +26889,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>43200</v>
+        <v>410400</v>
       </c>
       <c r="M13" t="n">
         <v>10500</v>
@@ -26901,10 +26901,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1021800</v>
+        <v>1287000</v>
       </c>
       <c r="Q13" t="n">
-        <v>119578.68</v>
+        <v>1172340</v>
       </c>
     </row>
     <row r="14">
@@ -26942,10 +26942,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16200</v>
+        <v>189000</v>
       </c>
       <c r="M14" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -26954,10 +26954,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>819000</v>
+        <v>762450</v>
       </c>
       <c r="Q14" t="n">
-        <v>80692.2</v>
+        <v>791100</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16200</v>
+        <v>226800</v>
       </c>
       <c r="M15" t="n">
-        <v>31500</v>
+        <v>21000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P15" t="n">
-        <v>1359150</v>
+        <v>2295150</v>
       </c>
       <c r="Q15" t="n">
-        <v>73146.24000000001</v>
+        <v>717120</v>
       </c>
     </row>
     <row r="16">
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5400</v>
+        <v>167400</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>308100</v>
+        <v>588900</v>
       </c>
       <c r="Q16" t="n">
-        <v>16854.48</v>
+        <v>165240</v>
       </c>
     </row>
     <row r="17">
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5850</v>
       </c>
       <c r="Q17" t="n">
-        <v>3635.28</v>
+        <v>35640</v>
       </c>
     </row>
     <row r="18">
@@ -27169,7 +27169,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>55.08</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19">
@@ -27692,7 +27692,7 @@
         <v>110610</v>
       </c>
       <c r="H4" t="n">
-        <v>28410</v>
+        <v>29880</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>66</v>
       </c>
       <c r="L4" t="n">
-        <v>309930</v>
+        <v>360900</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>79800</v>
+        <v>84360</v>
       </c>
       <c r="P4" t="n">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>29769.43</v>
+        <v>414511.02</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>54210</v>
       </c>
       <c r="H5" t="n">
-        <v>18750</v>
+        <v>20730</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>117480</v>
+        <v>131850</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>43020</v>
+        <v>49920</v>
       </c>
       <c r="P5" t="n">
-        <v>2760</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9892.43</v>
+        <v>137742.66</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>11010</v>
       </c>
       <c r="H6" t="n">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>25950</v>
+        <v>33330</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>14850</v>
+        <v>19260</v>
       </c>
       <c r="P6" t="n">
-        <v>3810</v>
+        <v>420</v>
       </c>
       <c r="Q6" t="n">
-        <v>1637.08</v>
+        <v>22794.75</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>630</v>
       </c>
       <c r="H7" t="n">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5130</v>
+        <v>6780</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>4110</v>
+        <v>11250</v>
       </c>
       <c r="P7" t="n">
-        <v>4950</v>
+        <v>1140</v>
       </c>
       <c r="Q7" t="n">
-        <v>151.73</v>
+        <v>2112.66</v>
       </c>
     </row>
     <row r="8">
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>750</v>
+        <v>2490</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1320</v>
+        <v>5070</v>
       </c>
       <c r="P8" t="n">
-        <v>5730</v>
+        <v>4350</v>
       </c>
       <c r="Q8" t="n">
-        <v>28.44</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>450</v>
+        <v>2340</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>150</v>
+        <v>1590</v>
       </c>
       <c r="P9" t="n">
-        <v>5130</v>
+        <v>10650</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.09</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>30</v>
+        <v>1380</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2460</v>
+        <v>7260</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1020</v>
+        <v>3600</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12">
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>120</v>
+        <v>660</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6750</v>
+        <v>7462.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>5.96</v>
       </c>
       <c r="L5" t="n">
-        <v>24670.8</v>
+        <v>27688.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2151</v>
+        <v>2496</v>
       </c>
       <c r="P5" t="n">
-        <v>55.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>494.62</v>
+        <v>6887.13</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>550.5</v>
       </c>
       <c r="H6" t="n">
-        <v>684</v>
+        <v>889.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>9601.5</v>
+        <v>12332.1</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3712.5</v>
+        <v>4815</v>
       </c>
       <c r="P6" t="n">
-        <v>571.5</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
-        <v>1227.81</v>
+        <v>17096.06</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>94.5</v>
       </c>
       <c r="H7" t="n">
-        <v>306.6</v>
+        <v>350.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3078</v>
+        <v>4068</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1438.5</v>
+        <v>3937.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1237.5</v>
+        <v>285</v>
       </c>
       <c r="Q7" t="n">
-        <v>121.38</v>
+        <v>1690.13</v>
       </c>
     </row>
     <row r="8">
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>532.5</v>
+        <v>1767.9</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>594</v>
+        <v>2281.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2177.4</v>
+        <v>1653</v>
       </c>
       <c r="Q8" t="n">
-        <v>27.02</v>
+        <v>376.2</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>364.5</v>
+        <v>1895.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>82.5</v>
+        <v>874.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2565</v>
+        <v>5325</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.72</v>
+        <v>163.25</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.7</v>
+        <v>1228.2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29326,10 +29326,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2091</v>
+        <v>6171</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.63</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>918</v>
+        <v>3240</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.36</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="12">
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>120</v>
+        <v>660</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13">
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>38475000</v>
+        <v>42537960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>289296.65</v>
       </c>
       <c r="L5" t="n">
-        <v>4440744</v>
+        <v>4983930</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>365670</v>
+        <v>424320</v>
       </c>
       <c r="P5" t="n">
-        <v>3588</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>296772.82</v>
+        <v>4132279.8</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>29727</v>
       </c>
       <c r="H6" t="n">
-        <v>3898800</v>
+        <v>5068440</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>1728270</v>
+        <v>2219778</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>631125</v>
+        <v>818550</v>
       </c>
       <c r="P6" t="n">
-        <v>37147.5</v>
+        <v>4095</v>
       </c>
       <c r="Q6" t="n">
-        <v>736684.88</v>
+        <v>10257637.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>5103</v>
       </c>
       <c r="H7" t="n">
-        <v>1747620</v>
+        <v>1997280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>554040</v>
+        <v>732240</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>244545</v>
+        <v>669375</v>
       </c>
       <c r="P7" t="n">
-        <v>80437.5</v>
+        <v>18525</v>
       </c>
       <c r="Q7" t="n">
-        <v>72829.14999999999</v>
+        <v>1014076.8</v>
       </c>
     </row>
     <row r="8">
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>95850</v>
+        <v>318222</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>100980</v>
+        <v>387855</v>
       </c>
       <c r="P8" t="n">
-        <v>141531</v>
+        <v>107445</v>
       </c>
       <c r="Q8" t="n">
-        <v>16210.8</v>
+        <v>225720</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>171000</v>
+        <v>1197000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>65610</v>
+        <v>341172</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>14025</v>
+        <v>148665</v>
       </c>
       <c r="P9" t="n">
-        <v>166725</v>
+        <v>346125</v>
       </c>
       <c r="Q9" t="n">
-        <v>7034.63</v>
+        <v>97950.60000000001</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4806</v>
+        <v>221076</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30618,10 +30618,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>135915</v>
+        <v>401115</v>
       </c>
       <c r="Q10" t="n">
-        <v>1578.42</v>
+        <v>21978</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>129600</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>59670</v>
+        <v>210600</v>
       </c>
       <c r="Q11" t="n">
-        <v>213.3</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="12">
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>7800</v>
+        <v>42900</v>
       </c>
       <c r="Q12" t="n">
-        <v>42.66</v>
+        <v>594</v>
       </c>
     </row>
     <row r="13">
